--- a/exports/data.xlsx
+++ b/exports/data.xlsx
@@ -35,54 +35,57 @@
     <t>Обновлено</t>
   </si>
   <si>
-    <t>Текст категория • Женщины</t>
+    <t>Текст категория • Юниоры 17-18</t>
   </si>
   <si>
     <t>КРУГ 11/85</t>
   </si>
   <si>
-    <t>КРИСТИНА ИЛЬИНА</t>
+    <t>ВСЕВОЛОД БОЙЧУК</t>
+  </si>
+  <si>
+    <t>1:04:09</t>
+  </si>
+  <si>
+    <t>2026-08-08T01:08:09.743Z</t>
+  </si>
+  <si>
+    <t>Место</t>
+  </si>
+  <si>
+    <t>Участник</t>
+  </si>
+  <si>
+    <t>Номер</t>
+  </si>
+  <si>
+    <t>Возраст</t>
+  </si>
+  <si>
+    <t>Клуб</t>
+  </si>
+  <si>
+    <t>Результат</t>
+  </si>
+  <si>
+    <t>До лидера</t>
+  </si>
+  <si>
+    <t>Ильина Кристина</t>
+  </si>
+  <si>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>26 лет</t>
+  </si>
+  <si>
+    <t>Челябинская область</t>
   </si>
   <si>
     <t>1:18:52</t>
   </si>
   <si>
-    <t>2026-08-08T16:10:28.028Z</t>
-  </si>
-  <si>
-    <t>Место</t>
-  </si>
-  <si>
-    <t>Участник</t>
-  </si>
-  <si>
-    <t>Номер</t>
-  </si>
-  <si>
-    <t>Возраст</t>
-  </si>
-  <si>
-    <t>Клуб</t>
-  </si>
-  <si>
-    <t>Результат</t>
-  </si>
-  <si>
-    <t>До лидера</t>
-  </si>
-  <si>
-    <t>Ильина Кристина</t>
-  </si>
-  <si>
-    <t>10003</t>
-  </si>
-  <si>
-    <t>26 лет</t>
-  </si>
-  <si>
-    <t>Челябинская область</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -858,9 +861,6 @@
   </si>
   <si>
     <t>1002</t>
-  </si>
-  <si>
-    <t>1:04:09</t>
   </si>
   <si>
     <t>Гвоздарев Вадим</t>
@@ -1632,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>10003</v>
+        <v>1002</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1692,10 +1692,10 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1703,22 +1703,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1726,22 +1726,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1749,22 +1749,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1772,22 +1772,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1795,22 +1795,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1818,22 +1818,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1841,22 +1841,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1864,22 +1864,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1887,22 +1887,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1910,22 +1910,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1933,22 +1933,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1956,22 +1956,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1979,22 +1979,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2002,22 +2002,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2025,22 +2025,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2048,22 +2048,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2071,22 +2071,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2094,22 +2094,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2117,22 +2117,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2140,22 +2140,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2197,22 +2197,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2220,22 +2220,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2243,22 +2243,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2266,22 +2266,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2289,22 +2289,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2312,22 +2312,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2335,22 +2335,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2358,22 +2358,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2381,22 +2381,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2404,22 +2404,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2427,22 +2427,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2450,22 +2450,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2473,22 +2473,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2496,22 +2496,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2519,22 +2519,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2542,22 +2542,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2565,22 +2565,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2588,22 +2588,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2611,22 +2611,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2634,22 +2634,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2657,22 +2657,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2680,22 +2680,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2737,22 +2737,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2760,22 +2760,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2783,22 +2783,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2806,22 +2806,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2829,22 +2829,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2852,22 +2852,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2875,22 +2875,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2898,22 +2898,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2921,22 +2921,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2944,22 +2944,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2967,22 +2967,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2990,22 +2990,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3013,22 +3013,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3036,22 +3036,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3059,22 +3059,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3082,22 +3082,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -3139,22 +3139,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>281</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3168,10 +3168,10 @@
         <v>283</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
         <v>284</v>
@@ -3191,10 +3191,10 @@
         <v>287</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
         <v>288</v>
@@ -3214,10 +3214,10 @@
         <v>291</v>
       </c>
       <c r="D5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
         <v>292</v>
@@ -3237,10 +3237,10 @@
         <v>295</v>
       </c>
       <c r="D6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
         <v>296</v>
@@ -3260,10 +3260,10 @@
         <v>299</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
         <v>300</v>
@@ -3283,10 +3283,10 @@
         <v>303</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F8" t="s">
         <v>304</v>
@@ -3306,10 +3306,10 @@
         <v>307</v>
       </c>
       <c r="D9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>308</v>
@@ -3329,7 +3329,7 @@
         <v>311</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -3352,10 +3352,10 @@
         <v>315</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>316</v>
@@ -3375,7 +3375,7 @@
         <v>319</v>
       </c>
       <c r="D12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E12" t="s">
         <v>320</v>
@@ -3398,10 +3398,10 @@
         <v>324</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
         <v>325</v>
@@ -3421,10 +3421,10 @@
         <v>328</v>
       </c>
       <c r="D14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
         <v>329</v>
@@ -3444,10 +3444,10 @@
         <v>331</v>
       </c>
       <c r="D15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
         <v>332</v>
@@ -3467,10 +3467,10 @@
         <v>335</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
         <v>336</v>
@@ -3490,10 +3490,10 @@
         <v>339</v>
       </c>
       <c r="D17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
         <v>340</v>
@@ -3513,10 +3513,10 @@
         <v>343</v>
       </c>
       <c r="D18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
         <v>344</v>
@@ -3536,10 +3536,10 @@
         <v>347</v>
       </c>
       <c r="D19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" t="s">
         <v>348</v>
@@ -3559,10 +3559,10 @@
         <v>351</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
         <v>352</v>
@@ -3582,10 +3582,10 @@
         <v>355</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F21" t="s">
         <v>356</v>
@@ -3605,13 +3605,13 @@
         <v>359</v>
       </c>
       <c r="D22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G22" t="s">
         <v>360</v>
@@ -3628,10 +3628,10 @@
         <v>362</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
         <v>363</v>
@@ -3651,10 +3651,10 @@
         <v>366</v>
       </c>
       <c r="D24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
         <v>367</v>
@@ -3674,10 +3674,10 @@
         <v>370</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F25" t="s">
         <v>371</v>
@@ -3697,10 +3697,10 @@
         <v>374</v>
       </c>
       <c r="D26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
         <v>375</v>
@@ -3720,10 +3720,10 @@
         <v>378</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F27" t="s">
         <v>379</v>
@@ -3743,10 +3743,10 @@
         <v>382</v>
       </c>
       <c r="D28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
         <v>383</v>
@@ -3766,10 +3766,10 @@
         <v>386</v>
       </c>
       <c r="D29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F29" t="s">
         <v>387</v>
@@ -3789,10 +3789,10 @@
         <v>390</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
         <v>391</v>
@@ -3812,10 +3812,10 @@
         <v>394</v>
       </c>
       <c r="D31" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>395</v>
@@ -3835,10 +3835,10 @@
         <v>398</v>
       </c>
       <c r="D32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F32" t="s">
         <v>399</v>

--- a/exports/data.xlsx
+++ b/exports/data.xlsx
@@ -47,7 +47,7 @@
     <t>1:04:47</t>
   </si>
   <si>
-    <t>2026-08-02T19:56:19.498Z</t>
+    <t>2026-08-08T13:44:56.387Z</t>
   </si>
   <si>
     <t>Место</t>

--- a/exports/data.xlsx
+++ b/exports/data.xlsx
@@ -47,7 +47,7 @@
     <t>1:04:47</t>
   </si>
   <si>
-    <t>2026-08-08T13:44:56.387Z</t>
+    <t>2026-08-08T13:46:15.929Z</t>
   </si>
   <si>
     <t>Место</t>

--- a/exports/data.xlsx
+++ b/exports/data.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Эфир" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Женщины" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Мужчины" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Юниорки 17-18" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Юниоры 17-18" state="visible" r:id="rId8"/>
+    <sheet sheetId="2" name="Текст категория • Женщины" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Текст категория • Мужчины" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Текст категория • Юниорки 17-18" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Текст категория • Юниоры 17-18" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="401">
   <si>
     <t>Категория</t>
   </si>
@@ -35,513 +35,648 @@
     <t>Обновлено</t>
   </si>
   <si>
-    <t>Юниорки 17-18</t>
-  </si>
-  <si>
-    <t>КРУГ 9/4</t>
-  </si>
-  <si>
-    <t>ЭЛИНА СЕМЕНОВА</t>
+    <t>Текст категория • Женщины</t>
+  </si>
+  <si>
+    <t>КРУГ 11</t>
+  </si>
+  <si>
+    <t>КРИСТИНА ИЛЬИНА</t>
+  </si>
+  <si>
+    <t>1:18:52</t>
+  </si>
+  <si>
+    <t>2026-08-08T15:21:26.387Z</t>
+  </si>
+  <si>
+    <t>Место</t>
+  </si>
+  <si>
+    <t>Участник</t>
+  </si>
+  <si>
+    <t>Номер</t>
+  </si>
+  <si>
+    <t>Возраст</t>
+  </si>
+  <si>
+    <t>Клуб</t>
+  </si>
+  <si>
+    <t>Результат</t>
+  </si>
+  <si>
+    <t>До лидера</t>
+  </si>
+  <si>
+    <t>Ильина Кристина</t>
+  </si>
+  <si>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>26 лет</t>
+  </si>
+  <si>
+    <t>Челябинская область</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Сайтарова Татьяна</t>
+  </si>
+  <si>
+    <t>10007</t>
+  </si>
+  <si>
+    <t>23 года</t>
+  </si>
+  <si>
+    <t>г. Москва</t>
+  </si>
+  <si>
+    <t>1:20:35</t>
+  </si>
+  <si>
+    <t>+1:43</t>
+  </si>
+  <si>
+    <t>Ушакова Александра</t>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>25 лет</t>
+  </si>
+  <si>
+    <t>Московская область</t>
+  </si>
+  <si>
+    <t>1:21:55</t>
+  </si>
+  <si>
+    <t>+3:03</t>
+  </si>
+  <si>
+    <t>Лунде Надежда</t>
+  </si>
+  <si>
+    <t>10004</t>
+  </si>
+  <si>
+    <t>г. Санкт-Петербург</t>
+  </si>
+  <si>
+    <t>1:25:14</t>
+  </si>
+  <si>
+    <t>+6:22</t>
+  </si>
+  <si>
+    <t>Тисленко Елизавета</t>
+  </si>
+  <si>
+    <t>10006</t>
+  </si>
+  <si>
+    <t>20 лет</t>
+  </si>
+  <si>
+    <t>Самарская область</t>
+  </si>
+  <si>
+    <t>1:25:43</t>
+  </si>
+  <si>
+    <t>+6:51</t>
+  </si>
+  <si>
+    <t>Миролюбова Анна</t>
+  </si>
+  <si>
+    <t>10013</t>
+  </si>
+  <si>
+    <t>Удмуртская Республика</t>
+  </si>
+  <si>
+    <t>1:26:47</t>
+  </si>
+  <si>
+    <t>+7:55</t>
+  </si>
+  <si>
+    <t>Рогозина Дарья</t>
+  </si>
+  <si>
+    <t>10017</t>
+  </si>
+  <si>
+    <t>29 лет</t>
+  </si>
+  <si>
+    <t>Чувашская Республика</t>
+  </si>
+  <si>
+    <t>1:26:56</t>
+  </si>
+  <si>
+    <t>+8:04</t>
+  </si>
+  <si>
+    <t>Калашникова Анна</t>
+  </si>
+  <si>
+    <t>10021</t>
+  </si>
+  <si>
+    <t>Республика Беларусь</t>
+  </si>
+  <si>
+    <t>1:29:26</t>
+  </si>
+  <si>
+    <t>+10:34</t>
+  </si>
+  <si>
+    <t>Тисленко Дарья</t>
+  </si>
+  <si>
+    <t>10009</t>
+  </si>
+  <si>
+    <t>1:30:17</t>
+  </si>
+  <si>
+    <t>+11:25</t>
+  </si>
+  <si>
+    <t>Карлова Алина</t>
+  </si>
+  <si>
+    <t>10002</t>
+  </si>
+  <si>
+    <t>21 год</t>
+  </si>
+  <si>
+    <t>1:32:04</t>
+  </si>
+  <si>
+    <t>+13:12</t>
+  </si>
+  <si>
+    <t>Менькова Дарья</t>
+  </si>
+  <si>
+    <t>10008</t>
+  </si>
+  <si>
+    <t>1:32:43</t>
+  </si>
+  <si>
+    <t>+13:51</t>
+  </si>
+  <si>
+    <t>Кирсанова Виктория</t>
+  </si>
+  <si>
+    <t>10014</t>
+  </si>
+  <si>
+    <t>1:11:14</t>
+  </si>
+  <si>
+    <t>-7:37</t>
+  </si>
+  <si>
+    <t>Гайбель Елизавета</t>
+  </si>
+  <si>
+    <t>10011</t>
+  </si>
+  <si>
+    <t>22 года</t>
+  </si>
+  <si>
+    <t>Свердловская область</t>
+  </si>
+  <si>
+    <t>1:13:03</t>
+  </si>
+  <si>
+    <t>-5:48</t>
+  </si>
+  <si>
+    <t>Калялина Анастасия</t>
+  </si>
+  <si>
+    <t>10010</t>
+  </si>
+  <si>
+    <t>28 лет</t>
+  </si>
+  <si>
+    <t>1:13:31</t>
+  </si>
+  <si>
+    <t>-5:20</t>
+  </si>
+  <si>
+    <t>Дудкина Карина</t>
+  </si>
+  <si>
+    <t>10018</t>
+  </si>
+  <si>
+    <t>18 лет</t>
+  </si>
+  <si>
+    <t>57:14</t>
+  </si>
+  <si>
+    <t>-21:37</t>
+  </si>
+  <si>
+    <t>Бавыкина Елизавета</t>
+  </si>
+  <si>
+    <t>10019</t>
+  </si>
+  <si>
+    <t>58:13</t>
+  </si>
+  <si>
+    <t>-20:38</t>
+  </si>
+  <si>
+    <t>Боредская Анастасия</t>
+  </si>
+  <si>
+    <t>10005</t>
+  </si>
+  <si>
+    <t>24 года</t>
+  </si>
+  <si>
+    <t>41:55</t>
+  </si>
+  <si>
+    <t>-36:56</t>
+  </si>
+  <si>
+    <t>Ахмадуллина Гузель</t>
+  </si>
+  <si>
+    <t>10020</t>
+  </si>
+  <si>
+    <t>31 год</t>
+  </si>
+  <si>
+    <t>42:03</t>
+  </si>
+  <si>
+    <t>-36:48</t>
+  </si>
+  <si>
+    <t>Гоголева Елена</t>
+  </si>
+  <si>
+    <t>10012</t>
+  </si>
+  <si>
+    <t>45 лет</t>
+  </si>
+  <si>
+    <t>44:31</t>
+  </si>
+  <si>
+    <t>-34:20</t>
+  </si>
+  <si>
+    <t>Тамонова Анна</t>
+  </si>
+  <si>
+    <t>10015</t>
+  </si>
+  <si>
+    <t>19 лет</t>
+  </si>
+  <si>
+    <t>44:45</t>
+  </si>
+  <si>
+    <t>-34:06</t>
+  </si>
+  <si>
+    <t>Кузнецова Анастасия</t>
+  </si>
+  <si>
+    <t>10016</t>
+  </si>
+  <si>
+    <t>28:16</t>
+  </si>
+  <si>
+    <t>-50:35</t>
+  </si>
+  <si>
+    <t>Синцов Антон</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>40 лет</t>
+  </si>
+  <si>
+    <t>1:24:32</t>
+  </si>
+  <si>
+    <t>Евграфов Евгений</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1:25:06</t>
+  </si>
+  <si>
+    <t>+0:33</t>
+  </si>
+  <si>
+    <t>Лужбин Илья</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1:25:50</t>
+  </si>
+  <si>
+    <t>+1:18</t>
+  </si>
+  <si>
+    <t>Лунде Павел</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>27 лет</t>
+  </si>
+  <si>
+    <t>1:27:07</t>
+  </si>
+  <si>
+    <t>+2:35</t>
+  </si>
+  <si>
+    <t>Шведов Ярослав</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1:27:46</t>
+  </si>
+  <si>
+    <t>+3:14</t>
+  </si>
+  <si>
+    <t>Иванов Николай</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1:28:03</t>
+  </si>
+  <si>
+    <t>+3:31</t>
+  </si>
+  <si>
+    <t>Осипов Даниил</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>1:28:22</t>
+  </si>
+  <si>
+    <t>+3:50</t>
+  </si>
+  <si>
+    <t>Балобанов Павел</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>1:29:55</t>
+  </si>
+  <si>
+    <t>+5:23</t>
+  </si>
+  <si>
+    <t>Москвин Данил</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>1:30:31</t>
+  </si>
+  <si>
+    <t>+5:59</t>
+  </si>
+  <si>
+    <t>Боредский Руслан</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1:31:13</t>
+  </si>
+  <si>
+    <t>+6:41</t>
+  </si>
+  <si>
+    <t>Филиппов Никита</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1:31:49</t>
+  </si>
+  <si>
+    <t>+7:17</t>
+  </si>
+  <si>
+    <t>Брицис Дайнис</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>1:33:12</t>
+  </si>
+  <si>
+    <t>+8:40</t>
+  </si>
+  <si>
+    <t>Селедков Иван</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>41 год</t>
+  </si>
+  <si>
+    <t>1:33:37</t>
+  </si>
+  <si>
+    <t>+9:04</t>
+  </si>
+  <si>
+    <t>Гоголев Максим</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>43 года</t>
+  </si>
+  <si>
+    <t>1:34:07</t>
+  </si>
+  <si>
+    <t>+9:35</t>
+  </si>
+  <si>
+    <t>Романов Иван</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1:35:00</t>
+  </si>
+  <si>
+    <t>+10:28</t>
+  </si>
+  <si>
+    <t>Марахтанов Глеб</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>1:07:49</t>
+  </si>
+  <si>
+    <t>-16:42</t>
+  </si>
+  <si>
+    <t>Малышко Максим</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>1:07:57</t>
+  </si>
+  <si>
+    <t>-16:34</t>
+  </si>
+  <si>
+    <t>Алексанин Данила</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>54:54</t>
+  </si>
+  <si>
+    <t>-29:37</t>
+  </si>
+  <si>
+    <t>Жидков Леон</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>55:46</t>
+  </si>
+  <si>
+    <t>-28:45</t>
+  </si>
+  <si>
+    <t>Кудрин Алексей</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>56:41</t>
+  </si>
+  <si>
+    <t>-27:50</t>
+  </si>
+  <si>
+    <t>Голубев Дмитрий</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>44:00</t>
+  </si>
+  <si>
+    <t>-40:31</t>
+  </si>
+  <si>
+    <t>Барнатович Владислав</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>30:44</t>
+  </si>
+  <si>
+    <t>-53:47</t>
+  </si>
+  <si>
+    <t>Семенова Элина</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>17 лет</t>
   </si>
   <si>
     <t>1:04:47</t>
   </si>
   <si>
-    <t>2026-08-08T13:46:15.929Z</t>
-  </si>
-  <si>
-    <t>Место</t>
-  </si>
-  <si>
-    <t>Участник</t>
-  </si>
-  <si>
-    <t>Номер</t>
-  </si>
-  <si>
-    <t>Возраст</t>
-  </si>
-  <si>
-    <t>Клуб</t>
-  </si>
-  <si>
-    <t>Результат</t>
-  </si>
-  <si>
-    <t>До лидера</t>
-  </si>
-  <si>
-    <t>Ильина Кристина</t>
-  </si>
-  <si>
-    <t>26 лет</t>
-  </si>
-  <si>
-    <t>Челябинская область</t>
-  </si>
-  <si>
-    <t>1:18:52</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Сайтарова Татьяна</t>
-  </si>
-  <si>
-    <t>23 года</t>
-  </si>
-  <si>
-    <t>г. Москва</t>
-  </si>
-  <si>
-    <t>1:20:35</t>
-  </si>
-  <si>
-    <t>+1:43</t>
-  </si>
-  <si>
-    <t>Ушакова Александра</t>
-  </si>
-  <si>
-    <t>25 лет</t>
-  </si>
-  <si>
-    <t>Московская область</t>
-  </si>
-  <si>
-    <t>1:21:55</t>
-  </si>
-  <si>
-    <t>+3:03</t>
-  </si>
-  <si>
-    <t>Лунде Надежда</t>
-  </si>
-  <si>
-    <t>г. Санкт-Петербург</t>
-  </si>
-  <si>
-    <t>1:25:14</t>
-  </si>
-  <si>
-    <t>+6:22</t>
-  </si>
-  <si>
-    <t>Тисленко Елизавета</t>
-  </si>
-  <si>
-    <t>20 лет</t>
-  </si>
-  <si>
-    <t>Самарская область</t>
-  </si>
-  <si>
-    <t>1:25:43</t>
-  </si>
-  <si>
-    <t>+6:51</t>
-  </si>
-  <si>
-    <t>Миролюбова Анна</t>
-  </si>
-  <si>
-    <t>Удмуртская Республика</t>
-  </si>
-  <si>
-    <t>1:26:47</t>
-  </si>
-  <si>
-    <t>+7:55</t>
-  </si>
-  <si>
-    <t>Рогозина Дарья</t>
-  </si>
-  <si>
-    <t>29 лет</t>
-  </si>
-  <si>
-    <t>Чувашская Республика</t>
-  </si>
-  <si>
-    <t>1:26:56</t>
-  </si>
-  <si>
-    <t>+8:04</t>
-  </si>
-  <si>
-    <t>Калашникова Анна</t>
-  </si>
-  <si>
-    <t>Республика Беларусь</t>
-  </si>
-  <si>
-    <t>1:29:26</t>
-  </si>
-  <si>
-    <t>+10:34</t>
-  </si>
-  <si>
-    <t>Тисленко Дарья</t>
-  </si>
-  <si>
-    <t>1:30:17</t>
-  </si>
-  <si>
-    <t>+11:25</t>
-  </si>
-  <si>
-    <t>Карлова Алина</t>
-  </si>
-  <si>
-    <t>21 год</t>
-  </si>
-  <si>
-    <t>1:32:04</t>
-  </si>
-  <si>
-    <t>+13:12</t>
-  </si>
-  <si>
-    <t>Менькова Дарья</t>
-  </si>
-  <si>
-    <t>1:32:43</t>
-  </si>
-  <si>
-    <t>+13:51</t>
-  </si>
-  <si>
-    <t>Кирсанова Виктория</t>
-  </si>
-  <si>
-    <t>1:11:14</t>
-  </si>
-  <si>
-    <t>-7:37</t>
-  </si>
-  <si>
-    <t>Гайбель Елизавета</t>
-  </si>
-  <si>
-    <t>22 года</t>
-  </si>
-  <si>
-    <t>Свердловская область</t>
-  </si>
-  <si>
-    <t>1:13:03</t>
-  </si>
-  <si>
-    <t>-5:48</t>
-  </si>
-  <si>
-    <t>Калялина Анастасия</t>
-  </si>
-  <si>
-    <t>28 лет</t>
-  </si>
-  <si>
-    <t>1:13:31</t>
-  </si>
-  <si>
-    <t>-5:20</t>
-  </si>
-  <si>
-    <t>Дудкина Карина</t>
-  </si>
-  <si>
-    <t>18 лет</t>
-  </si>
-  <si>
-    <t>57:14</t>
-  </si>
-  <si>
-    <t>-21:37</t>
-  </si>
-  <si>
-    <t>Бавыкина Елизавета</t>
-  </si>
-  <si>
-    <t>58:13</t>
-  </si>
-  <si>
-    <t>-20:38</t>
-  </si>
-  <si>
-    <t>Боредская Анастасия</t>
-  </si>
-  <si>
-    <t>24 года</t>
-  </si>
-  <si>
-    <t>41:55</t>
-  </si>
-  <si>
-    <t>-36:56</t>
-  </si>
-  <si>
-    <t>Ахмадуллина Гузель</t>
-  </si>
-  <si>
-    <t>31 год</t>
-  </si>
-  <si>
-    <t>42:03</t>
-  </si>
-  <si>
-    <t>-36:48</t>
-  </si>
-  <si>
-    <t>Гоголева Елена</t>
-  </si>
-  <si>
-    <t>45 лет</t>
-  </si>
-  <si>
-    <t>44:31</t>
-  </si>
-  <si>
-    <t>-34:20</t>
-  </si>
-  <si>
-    <t>Тамонова Анна</t>
-  </si>
-  <si>
-    <t>19 лет</t>
-  </si>
-  <si>
-    <t>44:45</t>
-  </si>
-  <si>
-    <t>-34:06</t>
-  </si>
-  <si>
-    <t>Кузнецова Анастасия</t>
-  </si>
-  <si>
-    <t>28:16</t>
-  </si>
-  <si>
-    <t>-50:35</t>
-  </si>
-  <si>
-    <t>Синцов Антон</t>
-  </si>
-  <si>
-    <t>40 лет</t>
-  </si>
-  <si>
-    <t>1:24:32</t>
-  </si>
-  <si>
-    <t>Евграфов Евгений</t>
-  </si>
-  <si>
-    <t>1:25:06</t>
-  </si>
-  <si>
-    <t>+0:33</t>
-  </si>
-  <si>
-    <t>Лужбин Илья</t>
-  </si>
-  <si>
-    <t>1:25:50</t>
-  </si>
-  <si>
-    <t>+1:18</t>
-  </si>
-  <si>
-    <t>Лунде Павел</t>
-  </si>
-  <si>
-    <t>27 лет</t>
-  </si>
-  <si>
-    <t>1:27:07</t>
-  </si>
-  <si>
-    <t>+2:35</t>
-  </si>
-  <si>
-    <t>Шведов Ярослав</t>
-  </si>
-  <si>
-    <t>1:27:46</t>
-  </si>
-  <si>
-    <t>+3:14</t>
-  </si>
-  <si>
-    <t>Иванов Николай</t>
-  </si>
-  <si>
-    <t>1:28:03</t>
-  </si>
-  <si>
-    <t>+3:31</t>
-  </si>
-  <si>
-    <t>Осипов Даниил</t>
-  </si>
-  <si>
-    <t>1:28:22</t>
-  </si>
-  <si>
-    <t>+3:50</t>
-  </si>
-  <si>
-    <t>Балобанов Павел</t>
-  </si>
-  <si>
-    <t>1:29:55</t>
-  </si>
-  <si>
-    <t>+5:23</t>
-  </si>
-  <si>
-    <t>Москвин Данил</t>
-  </si>
-  <si>
-    <t>1:30:31</t>
-  </si>
-  <si>
-    <t>+5:59</t>
-  </si>
-  <si>
-    <t>Боредский Руслан</t>
-  </si>
-  <si>
-    <t>1:31:13</t>
-  </si>
-  <si>
-    <t>+6:41</t>
-  </si>
-  <si>
-    <t>Филиппов Никита</t>
-  </si>
-  <si>
-    <t>1:31:49</t>
-  </si>
-  <si>
-    <t>+7:17</t>
-  </si>
-  <si>
-    <t>Брицис Дайнис</t>
-  </si>
-  <si>
-    <t>1:33:12</t>
-  </si>
-  <si>
-    <t>+8:40</t>
-  </si>
-  <si>
-    <t>Селедков Иван</t>
-  </si>
-  <si>
-    <t>41 год</t>
-  </si>
-  <si>
-    <t>1:33:37</t>
-  </si>
-  <si>
-    <t>+9:04</t>
-  </si>
-  <si>
-    <t>Гоголев Максим</t>
-  </si>
-  <si>
-    <t>43 года</t>
-  </si>
-  <si>
-    <t>1:34:07</t>
-  </si>
-  <si>
-    <t>+9:35</t>
-  </si>
-  <si>
-    <t>Романов Иван</t>
-  </si>
-  <si>
-    <t>1:35:00</t>
-  </si>
-  <si>
-    <t>+10:28</t>
-  </si>
-  <si>
-    <t>Марахтанов Глеб</t>
-  </si>
-  <si>
-    <t>1:07:49</t>
-  </si>
-  <si>
-    <t>-16:42</t>
-  </si>
-  <si>
-    <t>Малышко Максим</t>
-  </si>
-  <si>
-    <t>1:07:57</t>
-  </si>
-  <si>
-    <t>-16:34</t>
-  </si>
-  <si>
-    <t>Алексанин Данила</t>
-  </si>
-  <si>
-    <t>54:54</t>
-  </si>
-  <si>
-    <t>-29:37</t>
-  </si>
-  <si>
-    <t>Жидков Леон</t>
-  </si>
-  <si>
-    <t>55:46</t>
-  </si>
-  <si>
-    <t>-28:45</t>
-  </si>
-  <si>
-    <t>Кудрин Алексей</t>
-  </si>
-  <si>
-    <t>56:41</t>
-  </si>
-  <si>
-    <t>-27:50</t>
-  </si>
-  <si>
-    <t>Голубев Дмитрий</t>
-  </si>
-  <si>
-    <t>44:00</t>
-  </si>
-  <si>
-    <t>-40:31</t>
-  </si>
-  <si>
-    <t>Барнатович Владислав</t>
-  </si>
-  <si>
-    <t>30:44</t>
-  </si>
-  <si>
-    <t>-53:47</t>
-  </si>
-  <si>
-    <t>Семенова Элина</t>
-  </si>
-  <si>
-    <t>17 лет</t>
-  </si>
-  <si>
     <t>Тимошенко Полина</t>
   </si>
   <si>
+    <t>109</t>
+  </si>
+  <si>
     <t>1:06:02</t>
   </si>
   <si>
@@ -551,6 +686,9 @@
     <t>Викторова Виктория</t>
   </si>
   <si>
+    <t>108</t>
+  </si>
+  <si>
     <t>1:07:56</t>
   </si>
   <si>
@@ -560,6 +698,9 @@
     <t>Зорина Марина</t>
   </si>
   <si>
+    <t>104</t>
+  </si>
+  <si>
     <t>1:08:39</t>
   </si>
   <si>
@@ -569,6 +710,9 @@
     <t>Аветисова Ксения</t>
   </si>
   <si>
+    <t>105</t>
+  </si>
+  <si>
     <t>1:09:07</t>
   </si>
   <si>
@@ -578,6 +722,9 @@
     <t>Келлер Софья</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>1:09:20</t>
   </si>
   <si>
@@ -587,6 +734,9 @@
     <t>Сухорученкова Мария</t>
   </si>
   <si>
+    <t>102</t>
+  </si>
+  <si>
     <t>1:10:31</t>
   </si>
   <si>
@@ -596,6 +746,9 @@
     <t>Картинина Дарья</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>1:14:49</t>
   </si>
   <si>
@@ -605,6 +758,9 @@
     <t>Парусова Елена</t>
   </si>
   <si>
+    <t>103</t>
+  </si>
+  <si>
     <t>1:17:29</t>
   </si>
   <si>
@@ -614,6 +770,9 @@
     <t>Ростовщикова София</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>56:40</t>
   </si>
   <si>
@@ -623,6 +782,9 @@
     <t>Никитина Кристина</t>
   </si>
   <si>
+    <t>115</t>
+  </si>
+  <si>
     <t>16 лет</t>
   </si>
   <si>
@@ -635,6 +797,9 @@
     <t>Чернышева Карина</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>1:01:07</t>
   </si>
   <si>
@@ -644,6 +809,9 @@
     <t>Косарева Арина</t>
   </si>
   <si>
+    <t>107</t>
+  </si>
+  <si>
     <t>42:13</t>
   </si>
   <si>
@@ -653,6 +821,9 @@
     <t>Пинегина Александра</t>
   </si>
   <si>
+    <t>106</t>
+  </si>
+  <si>
     <t>43:01</t>
   </si>
   <si>
@@ -662,6 +833,9 @@
     <t>Егорова Виктория</t>
   </si>
   <si>
+    <t>116</t>
+  </si>
+  <si>
     <t>43:36</t>
   </si>
   <si>
@@ -671,6 +845,9 @@
     <t>Гармаш Анастасия</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>28:34</t>
   </si>
   <si>
@@ -680,12 +857,18 @@
     <t>Бойчук Всеволод</t>
   </si>
   <si>
+    <t>1002</t>
+  </si>
+  <si>
     <t>1:04:09</t>
   </si>
   <si>
     <t>Гвоздарев Вадим</t>
   </si>
   <si>
+    <t>1003</t>
+  </si>
+  <si>
     <t>1:05:02</t>
   </si>
   <si>
@@ -695,6 +878,9 @@
     <t>Титов Егор</t>
   </si>
   <si>
+    <t>1007</t>
+  </si>
+  <si>
     <t>1:06:55</t>
   </si>
   <si>
@@ -704,6 +890,9 @@
     <t>Логачев Илья</t>
   </si>
   <si>
+    <t>1009</t>
+  </si>
+  <si>
     <t>1:08:14</t>
   </si>
   <si>
@@ -713,6 +902,9 @@
     <t>Рычков Илья</t>
   </si>
   <si>
+    <t>1008</t>
+  </si>
+  <si>
     <t>1:10:48</t>
   </si>
   <si>
@@ -722,6 +914,9 @@
     <t>Петров Никита</t>
   </si>
   <si>
+    <t>1001</t>
+  </si>
+  <si>
     <t>1:11:21</t>
   </si>
   <si>
@@ -731,6 +926,9 @@
     <t>Захаров Тимур</t>
   </si>
   <si>
+    <t>1011</t>
+  </si>
+  <si>
     <t>1:11:51</t>
   </si>
   <si>
@@ -740,6 +938,9 @@
     <t>Серяков Кирилл</t>
   </si>
   <si>
+    <t>1020</t>
+  </si>
+  <si>
     <t>1:12:07</t>
   </si>
   <si>
@@ -749,6 +950,9 @@
     <t>Власов Александр</t>
   </si>
   <si>
+    <t>1012</t>
+  </si>
+  <si>
     <t>1:13:27</t>
   </si>
   <si>
@@ -758,6 +962,9 @@
     <t>Рыжанков Никита</t>
   </si>
   <si>
+    <t>1030</t>
+  </si>
+  <si>
     <t>1:13:47</t>
   </si>
   <si>
@@ -767,6 +974,9 @@
     <t>Пермяков Игорь</t>
   </si>
   <si>
+    <t>1026</t>
+  </si>
+  <si>
     <t>Пермский край</t>
   </si>
   <si>
@@ -779,6 +989,9 @@
     <t>Масликов Кирилл</t>
   </si>
   <si>
+    <t>1010</t>
+  </si>
+  <si>
     <t>1:14:19</t>
   </si>
   <si>
@@ -788,12 +1001,18 @@
     <t>Кынев Захар</t>
   </si>
   <si>
+    <t>1017</t>
+  </si>
+  <si>
     <t>1:14:20</t>
   </si>
   <si>
     <t>Евдокимов Павел</t>
   </si>
   <si>
+    <t>1015</t>
+  </si>
+  <si>
     <t>1:14:22</t>
   </si>
   <si>
@@ -803,6 +1022,9 @@
     <t>Цветков Семен</t>
   </si>
   <si>
+    <t>1023</t>
+  </si>
+  <si>
     <t>1:16:54</t>
   </si>
   <si>
@@ -812,6 +1034,9 @@
     <t>Синюкович Данила</t>
   </si>
   <si>
+    <t>1016</t>
+  </si>
+  <si>
     <t>1:15:27</t>
   </si>
   <si>
@@ -821,6 +1046,9 @@
     <t>Мигунов Максим</t>
   </si>
   <si>
+    <t>1014</t>
+  </si>
+  <si>
     <t>58:46</t>
   </si>
   <si>
@@ -830,6 +1058,9 @@
     <t>Кибардин Вадим</t>
   </si>
   <si>
+    <t>1024</t>
+  </si>
+  <si>
     <t>59:33</t>
   </si>
   <si>
@@ -839,6 +1070,9 @@
     <t>Погореловский Вячеслав</t>
   </si>
   <si>
+    <t>1005</t>
+  </si>
+  <si>
     <t>59:51</t>
   </si>
   <si>
@@ -848,6 +1082,9 @@
     <t>Еруженец Георгий</t>
   </si>
   <si>
+    <t>1025</t>
+  </si>
+  <si>
     <t>1:00:04</t>
   </si>
   <si>
@@ -857,12 +1094,18 @@
     <t>Петров Тимофей</t>
   </si>
   <si>
+    <t>1019</t>
+  </si>
+  <si>
     <t>-3:52</t>
   </si>
   <si>
     <t>Клишин Семен</t>
   </si>
   <si>
+    <t>1004</t>
+  </si>
+  <si>
     <t>1:00:24</t>
   </si>
   <si>
@@ -872,6 +1115,9 @@
     <t>Зацепин Юрий</t>
   </si>
   <si>
+    <t>1021</t>
+  </si>
+  <si>
     <t>1:00:31</t>
   </si>
   <si>
@@ -881,6 +1127,9 @@
     <t>Гимранов Антон</t>
   </si>
   <si>
+    <t>1027</t>
+  </si>
+  <si>
     <t>1:01:57</t>
   </si>
   <si>
@@ -890,6 +1139,9 @@
     <t>Матвеев Никита</t>
   </si>
   <si>
+    <t>1013</t>
+  </si>
+  <si>
     <t>46:52</t>
   </si>
   <si>
@@ -899,6 +1151,9 @@
     <t>Демин Глеб</t>
   </si>
   <si>
+    <t>1029</t>
+  </si>
+  <si>
     <t>46:04</t>
   </si>
   <si>
@@ -908,6 +1163,9 @@
     <t>Кузьмин Всеволод</t>
   </si>
   <si>
+    <t>1018</t>
+  </si>
+  <si>
     <t>46:19</t>
   </si>
   <si>
@@ -917,6 +1175,9 @@
     <t>Лопатин Александр</t>
   </si>
   <si>
+    <t>1028</t>
+  </si>
+  <si>
     <t>47:43</t>
   </si>
   <si>
@@ -926,6 +1187,9 @@
     <t>Дмитриев Даниил</t>
   </si>
   <si>
+    <t>1006</t>
+  </si>
+  <si>
     <t>50:01</t>
   </si>
   <si>
@@ -935,6 +1199,9 @@
     <t>Клишковский Артем</t>
   </si>
   <si>
+    <t>1022</t>
+  </si>
+  <si>
     <t>34:34</t>
   </si>
   <si>
@@ -942,6 +1209,9 @@
   </si>
   <si>
     <t>Тебеньков Всеволод</t>
+  </si>
+  <si>
+    <t>1031</t>
   </si>
   <si>
     <t>3:10</t>
@@ -1362,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>101</v>
+        <v>10003</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1412,17 +1682,17 @@
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2">
-        <v>10003</v>
+      <c r="C2" t="s">
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -1435,20 +1705,20 @@
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3">
-        <v>10007</v>
+      <c r="C3" t="s">
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1456,22 +1726,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4">
-        <v>10001</v>
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1479,22 +1749,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5">
-        <v>10004</v>
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1502,22 +1772,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6">
-        <v>10006</v>
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1525,22 +1795,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7">
-        <v>10013</v>
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1548,22 +1818,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8">
-        <v>10017</v>
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1571,22 +1841,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9">
-        <v>10021</v>
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1594,22 +1864,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10">
-        <v>10009</v>
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1617,22 +1887,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11">
-        <v>10002</v>
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G11" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1640,22 +1910,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12">
-        <v>10008</v>
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1663,22 +1933,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13">
-        <v>10014</v>
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1686,22 +1956,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14">
-        <v>10011</v>
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1709,22 +1979,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15">
-        <v>10010</v>
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1732,22 +2002,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16">
-        <v>10018</v>
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1755,22 +2025,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17">
-        <v>10019</v>
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1778,22 +2048,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18">
-        <v>10005</v>
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="G18" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1801,22 +2071,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19">
-        <v>10020</v>
+        <v>104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="G19" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1824,22 +2094,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20">
-        <v>10012</v>
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="G20" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1847,22 +2117,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21">
-        <v>10015</v>
+        <v>114</v>
+      </c>
+      <c r="C21" t="s">
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="G21" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1870,22 +2140,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22">
-        <v>10016</v>
+        <v>119</v>
+      </c>
+      <c r="C22" t="s">
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1927,19 +2197,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2">
-        <v>23</v>
+        <v>123</v>
+      </c>
+      <c r="C2" t="s">
+        <v>124</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -1950,22 +2220,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
+        <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="G3" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1973,22 +2243,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
+        <v>131</v>
+      </c>
+      <c r="C4" t="s">
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="G4" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1996,22 +2266,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
+        <v>135</v>
+      </c>
+      <c r="C5" t="s">
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="G5" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2019,22 +2289,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
+        <v>140</v>
+      </c>
+      <c r="C6" t="s">
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="G6" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2042,22 +2312,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
+        <v>144</v>
+      </c>
+      <c r="C7" t="s">
+        <v>145</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2065,22 +2335,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
+        <v>148</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="G8" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2088,22 +2358,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9">
-        <v>11</v>
+        <v>152</v>
+      </c>
+      <c r="C9" t="s">
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="G9" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2111,22 +2381,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10">
-        <v>13</v>
+        <v>156</v>
+      </c>
+      <c r="C10" t="s">
+        <v>157</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="G10" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2134,22 +2404,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
+        <v>160</v>
+      </c>
+      <c r="C11" t="s">
+        <v>161</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="G11" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2157,22 +2427,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12">
-        <v>9</v>
+        <v>164</v>
+      </c>
+      <c r="C12" t="s">
+        <v>165</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F12" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="G12" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2180,22 +2450,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13">
-        <v>14</v>
+        <v>168</v>
+      </c>
+      <c r="C13" t="s">
+        <v>169</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2203,22 +2473,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14">
-        <v>19</v>
+        <v>172</v>
+      </c>
+      <c r="C14" t="s">
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="G14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2226,22 +2496,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C15">
-        <v>7</v>
+        <v>177</v>
+      </c>
+      <c r="C15" t="s">
+        <v>178</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="G15" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2249,22 +2519,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
+        <v>182</v>
+      </c>
+      <c r="C16" t="s">
+        <v>183</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="G16" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2272,22 +2542,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C17">
-        <v>17</v>
+        <v>186</v>
+      </c>
+      <c r="C17" t="s">
+        <v>187</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F17" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="G17" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2295,22 +2565,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18">
-        <v>18</v>
+        <v>190</v>
+      </c>
+      <c r="C18" t="s">
+        <v>191</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="G18" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2318,22 +2588,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
-      </c>
-      <c r="C19">
-        <v>15</v>
+        <v>194</v>
+      </c>
+      <c r="C19" t="s">
+        <v>195</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="G19" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2341,22 +2611,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C20">
-        <v>12</v>
+        <v>198</v>
+      </c>
+      <c r="C20" t="s">
+        <v>199</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="G20" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2364,22 +2634,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>163</v>
-      </c>
-      <c r="C21">
-        <v>21</v>
+        <v>202</v>
+      </c>
+      <c r="C21" t="s">
+        <v>203</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="G21" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2387,22 +2657,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>166</v>
-      </c>
-      <c r="C22">
-        <v>20</v>
+        <v>206</v>
+      </c>
+      <c r="C22" t="s">
+        <v>207</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="G22" t="s">
-        <v>168</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2410,22 +2680,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>169</v>
-      </c>
-      <c r="C23">
-        <v>16</v>
+        <v>210</v>
+      </c>
+      <c r="C23" t="s">
+        <v>211</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F23" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="G23" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2467,19 +2737,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2">
-        <v>101</v>
+        <v>214</v>
+      </c>
+      <c r="C2" t="s">
+        <v>215</v>
       </c>
       <c r="D2" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>217</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -2490,22 +2760,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3">
-        <v>109</v>
+        <v>218</v>
+      </c>
+      <c r="C3" t="s">
+        <v>219</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="G3" t="s">
-        <v>176</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2513,22 +2783,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4">
-        <v>108</v>
+        <v>222</v>
+      </c>
+      <c r="C4" t="s">
+        <v>223</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="G4" t="s">
-        <v>179</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2536,22 +2806,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C5">
-        <v>104</v>
+        <v>226</v>
+      </c>
+      <c r="C5" t="s">
+        <v>227</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="G5" t="s">
-        <v>182</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2559,22 +2829,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6">
-        <v>105</v>
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>231</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>184</v>
+        <v>232</v>
       </c>
       <c r="G6" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2582,22 +2852,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C7">
-        <v>112</v>
+        <v>234</v>
+      </c>
+      <c r="C7" t="s">
+        <v>235</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>187</v>
+        <v>236</v>
       </c>
       <c r="G7" t="s">
-        <v>188</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2605,22 +2875,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
-      </c>
-      <c r="C8">
-        <v>102</v>
+        <v>238</v>
+      </c>
+      <c r="C8" t="s">
+        <v>239</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="G8" t="s">
-        <v>191</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2628,22 +2898,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9">
-        <v>111</v>
+        <v>242</v>
+      </c>
+      <c r="C9" t="s">
+        <v>243</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="G9" t="s">
-        <v>194</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2651,22 +2921,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
-      </c>
-      <c r="C10">
-        <v>103</v>
+        <v>246</v>
+      </c>
+      <c r="C10" t="s">
+        <v>247</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="G10" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2674,22 +2944,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
-      </c>
-      <c r="C11">
-        <v>110</v>
+        <v>250</v>
+      </c>
+      <c r="C11" t="s">
+        <v>251</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>199</v>
+        <v>252</v>
       </c>
       <c r="G11" t="s">
-        <v>200</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2697,22 +2967,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>201</v>
-      </c>
-      <c r="C12">
-        <v>115</v>
+        <v>254</v>
+      </c>
+      <c r="C12" t="s">
+        <v>255</v>
       </c>
       <c r="D12" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="G12" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2720,22 +2990,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>205</v>
-      </c>
-      <c r="C13">
-        <v>114</v>
+        <v>259</v>
+      </c>
+      <c r="C13" t="s">
+        <v>260</v>
       </c>
       <c r="D13" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
-        <v>206</v>
+        <v>261</v>
       </c>
       <c r="G13" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2743,22 +3013,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
-      </c>
-      <c r="C14">
-        <v>107</v>
+        <v>263</v>
+      </c>
+      <c r="C14" t="s">
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
-        <v>209</v>
+        <v>265</v>
       </c>
       <c r="G14" t="s">
-        <v>210</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2766,22 +3036,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>211</v>
-      </c>
-      <c r="C15">
-        <v>106</v>
+        <v>267</v>
+      </c>
+      <c r="C15" t="s">
+        <v>268</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="G15" t="s">
-        <v>213</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2789,22 +3059,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C16">
-        <v>116</v>
+        <v>271</v>
+      </c>
+      <c r="C16" t="s">
+        <v>272</v>
       </c>
       <c r="D16" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
-        <v>215</v>
+        <v>273</v>
       </c>
       <c r="G16" t="s">
-        <v>216</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2812,22 +3082,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>217</v>
-      </c>
-      <c r="C17">
-        <v>113</v>
+        <v>275</v>
+      </c>
+      <c r="C17" t="s">
+        <v>276</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F17" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="G17" t="s">
-        <v>219</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -2869,19 +3139,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C2">
-        <v>1002</v>
+        <v>279</v>
+      </c>
+      <c r="C2" t="s">
+        <v>280</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -2892,22 +3162,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C3">
-        <v>1003</v>
+        <v>282</v>
+      </c>
+      <c r="C3" t="s">
+        <v>283</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="G3" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2915,22 +3185,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4">
-        <v>1007</v>
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>287</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>226</v>
+        <v>288</v>
       </c>
       <c r="G4" t="s">
-        <v>227</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2938,22 +3208,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5">
-        <v>1009</v>
+        <v>290</v>
+      </c>
+      <c r="C5" t="s">
+        <v>291</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>229</v>
+        <v>292</v>
       </c>
       <c r="G5" t="s">
-        <v>230</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2961,22 +3231,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C6">
-        <v>1008</v>
+        <v>294</v>
+      </c>
+      <c r="C6" t="s">
+        <v>295</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="G6" t="s">
-        <v>233</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2984,22 +3254,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C7">
-        <v>1001</v>
+        <v>298</v>
+      </c>
+      <c r="C7" t="s">
+        <v>299</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="G7" t="s">
-        <v>236</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3007,22 +3277,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>237</v>
-      </c>
-      <c r="C8">
-        <v>1011</v>
+        <v>302</v>
+      </c>
+      <c r="C8" t="s">
+        <v>303</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F8" t="s">
-        <v>238</v>
+        <v>304</v>
       </c>
       <c r="G8" t="s">
-        <v>239</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3030,22 +3300,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9">
-        <v>1020</v>
+        <v>306</v>
+      </c>
+      <c r="C9" t="s">
+        <v>307</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="G9" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3053,22 +3323,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>243</v>
-      </c>
-      <c r="C10">
-        <v>1012</v>
+        <v>310</v>
+      </c>
+      <c r="C10" t="s">
+        <v>311</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="G10" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3076,22 +3346,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
-      </c>
-      <c r="C11">
-        <v>1030</v>
+        <v>314</v>
+      </c>
+      <c r="C11" t="s">
+        <v>315</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>247</v>
+        <v>316</v>
       </c>
       <c r="G11" t="s">
-        <v>248</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3099,22 +3369,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C12">
-        <v>1026</v>
+        <v>318</v>
+      </c>
+      <c r="C12" t="s">
+        <v>319</v>
       </c>
       <c r="D12" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="E12" t="s">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="F12" t="s">
-        <v>251</v>
+        <v>321</v>
       </c>
       <c r="G12" t="s">
-        <v>252</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3122,22 +3392,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>253</v>
-      </c>
-      <c r="C13">
-        <v>1010</v>
+        <v>323</v>
+      </c>
+      <c r="C13" t="s">
+        <v>324</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>254</v>
+        <v>325</v>
       </c>
       <c r="G13" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3145,22 +3415,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" t="s">
+        <v>328</v>
+      </c>
+      <c r="D14" t="s">
         <v>256</v>
       </c>
-      <c r="C14">
-        <v>1017</v>
-      </c>
-      <c r="D14" t="s">
-        <v>202</v>
-      </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>257</v>
+        <v>329</v>
       </c>
       <c r="G14" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3168,22 +3438,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
-      </c>
-      <c r="C15">
-        <v>1015</v>
+        <v>330</v>
+      </c>
+      <c r="C15" t="s">
+        <v>331</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="G15" t="s">
-        <v>260</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3191,22 +3461,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>261</v>
-      </c>
-      <c r="C16">
-        <v>1023</v>
+        <v>334</v>
+      </c>
+      <c r="C16" t="s">
+        <v>335</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
-        <v>262</v>
+        <v>336</v>
       </c>
       <c r="G16" t="s">
-        <v>263</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3214,22 +3484,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>264</v>
-      </c>
-      <c r="C17">
-        <v>1016</v>
+        <v>338</v>
+      </c>
+      <c r="C17" t="s">
+        <v>339</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F17" t="s">
-        <v>265</v>
+        <v>340</v>
       </c>
       <c r="G17" t="s">
-        <v>266</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3237,22 +3507,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>267</v>
-      </c>
-      <c r="C18">
-        <v>1014</v>
+        <v>342</v>
+      </c>
+      <c r="C18" t="s">
+        <v>343</v>
       </c>
       <c r="D18" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>268</v>
+        <v>344</v>
       </c>
       <c r="G18" t="s">
-        <v>269</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3260,22 +3530,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>270</v>
-      </c>
-      <c r="C19">
-        <v>1024</v>
+        <v>346</v>
+      </c>
+      <c r="C19" t="s">
+        <v>347</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s">
-        <v>271</v>
+        <v>348</v>
       </c>
       <c r="G19" t="s">
-        <v>272</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3283,22 +3553,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>273</v>
-      </c>
-      <c r="C20">
-        <v>1005</v>
+        <v>350</v>
+      </c>
+      <c r="C20" t="s">
+        <v>351</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>274</v>
+        <v>352</v>
       </c>
       <c r="G20" t="s">
-        <v>275</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3306,22 +3576,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>276</v>
-      </c>
-      <c r="C21">
-        <v>1025</v>
+        <v>354</v>
+      </c>
+      <c r="C21" t="s">
+        <v>355</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>277</v>
+        <v>356</v>
       </c>
       <c r="G21" t="s">
-        <v>278</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3329,22 +3599,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>279</v>
-      </c>
-      <c r="C22">
-        <v>1019</v>
+        <v>358</v>
+      </c>
+      <c r="C22" t="s">
+        <v>359</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="G22" t="s">
-        <v>280</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3352,22 +3622,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>281</v>
-      </c>
-      <c r="C23">
-        <v>1004</v>
+        <v>361</v>
+      </c>
+      <c r="C23" t="s">
+        <v>362</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>282</v>
+        <v>363</v>
       </c>
       <c r="G23" t="s">
-        <v>283</v>
+        <v>364</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3375,22 +3645,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>284</v>
-      </c>
-      <c r="C24">
-        <v>1021</v>
+        <v>365</v>
+      </c>
+      <c r="C24" t="s">
+        <v>366</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F24" t="s">
-        <v>285</v>
+        <v>367</v>
       </c>
       <c r="G24" t="s">
-        <v>286</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3398,22 +3668,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>287</v>
-      </c>
-      <c r="C25">
-        <v>1027</v>
+        <v>369</v>
+      </c>
+      <c r="C25" t="s">
+        <v>370</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s">
-        <v>288</v>
+        <v>371</v>
       </c>
       <c r="G25" t="s">
-        <v>289</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3421,22 +3691,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>290</v>
-      </c>
-      <c r="C26">
-        <v>1013</v>
+        <v>373</v>
+      </c>
+      <c r="C26" t="s">
+        <v>374</v>
       </c>
       <c r="D26" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F26" t="s">
-        <v>291</v>
+        <v>375</v>
       </c>
       <c r="G26" t="s">
-        <v>292</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3444,22 +3714,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>293</v>
-      </c>
-      <c r="C27">
-        <v>1029</v>
+        <v>377</v>
+      </c>
+      <c r="C27" t="s">
+        <v>378</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F27" t="s">
-        <v>294</v>
+        <v>379</v>
       </c>
       <c r="G27" t="s">
-        <v>295</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3467,22 +3737,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>296</v>
-      </c>
-      <c r="C28">
-        <v>1018</v>
+        <v>381</v>
+      </c>
+      <c r="C28" t="s">
+        <v>382</v>
       </c>
       <c r="D28" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F28" t="s">
-        <v>297</v>
+        <v>383</v>
       </c>
       <c r="G28" t="s">
-        <v>298</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3490,22 +3760,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>299</v>
-      </c>
-      <c r="C29">
-        <v>1028</v>
+        <v>385</v>
+      </c>
+      <c r="C29" t="s">
+        <v>386</v>
       </c>
       <c r="D29" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="E29" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F29" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="G29" t="s">
-        <v>301</v>
+        <v>388</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3513,22 +3783,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>302</v>
-      </c>
-      <c r="C30">
-        <v>1006</v>
+        <v>389</v>
+      </c>
+      <c r="C30" t="s">
+        <v>390</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F30" t="s">
-        <v>303</v>
+        <v>391</v>
       </c>
       <c r="G30" t="s">
-        <v>304</v>
+        <v>392</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3536,22 +3806,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>305</v>
-      </c>
-      <c r="C31">
-        <v>1022</v>
+        <v>393</v>
+      </c>
+      <c r="C31" t="s">
+        <v>394</v>
       </c>
       <c r="D31" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E31" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
-        <v>306</v>
+        <v>395</v>
       </c>
       <c r="G31" t="s">
-        <v>307</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3559,22 +3829,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>308</v>
-      </c>
-      <c r="C32">
-        <v>1031</v>
+        <v>397</v>
+      </c>
+      <c r="C32" t="s">
+        <v>398</v>
       </c>
       <c r="D32" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F32" t="s">
-        <v>309</v>
+        <v>399</v>
       </c>
       <c r="G32" t="s">
-        <v>310</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/exports/data.xlsx
+++ b/exports/data.xlsx
@@ -35,54 +35,57 @@
     <t>Обновлено</t>
   </si>
   <si>
-    <t>Текст категория • Женщины</t>
-  </si>
-  <si>
-    <t>КРУГ 11</t>
-  </si>
-  <si>
-    <t>КРИСТИНА ИЛЬИНА</t>
+    <t>Текст категория • Юниорки 17-18</t>
+  </si>
+  <si>
+    <t>КРУГ 9/85</t>
+  </si>
+  <si>
+    <t>ЭЛИНА СЕМЕНОВА</t>
+  </si>
+  <si>
+    <t>1:04:47</t>
+  </si>
+  <si>
+    <t>2026-08-08T15:38:54.273Z</t>
+  </si>
+  <si>
+    <t>Место</t>
+  </si>
+  <si>
+    <t>Участник</t>
+  </si>
+  <si>
+    <t>Номер</t>
+  </si>
+  <si>
+    <t>Возраст</t>
+  </si>
+  <si>
+    <t>Клуб</t>
+  </si>
+  <si>
+    <t>Результат</t>
+  </si>
+  <si>
+    <t>До лидера</t>
+  </si>
+  <si>
+    <t>Ильина Кристина</t>
+  </si>
+  <si>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>26 лет</t>
+  </si>
+  <si>
+    <t>Челябинская область</t>
   </si>
   <si>
     <t>1:18:52</t>
   </si>
   <si>
-    <t>2026-08-08T15:21:26.387Z</t>
-  </si>
-  <si>
-    <t>Место</t>
-  </si>
-  <si>
-    <t>Участник</t>
-  </si>
-  <si>
-    <t>Номер</t>
-  </si>
-  <si>
-    <t>Возраст</t>
-  </si>
-  <si>
-    <t>Клуб</t>
-  </si>
-  <si>
-    <t>Результат</t>
-  </si>
-  <si>
-    <t>До лидера</t>
-  </si>
-  <si>
-    <t>Ильина Кристина</t>
-  </si>
-  <si>
-    <t>10003</t>
-  </si>
-  <si>
-    <t>26 лет</t>
-  </si>
-  <si>
-    <t>Челябинская область</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -666,9 +669,6 @@
   </si>
   <si>
     <t>17 лет</t>
-  </si>
-  <si>
-    <t>1:04:47</t>
   </si>
   <si>
     <t>Тимошенко Полина</t>
@@ -1632,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>10003</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1692,10 +1692,10 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1703,22 +1703,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1726,22 +1726,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1749,22 +1749,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1772,22 +1772,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1795,22 +1795,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1818,22 +1818,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1841,22 +1841,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1864,22 +1864,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1887,22 +1887,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1910,22 +1910,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1933,22 +1933,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1956,22 +1956,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1979,22 +1979,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2002,22 +2002,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2025,22 +2025,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2048,22 +2048,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2071,22 +2071,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2094,22 +2094,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2117,22 +2117,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2140,22 +2140,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2197,22 +2197,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2220,22 +2220,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2243,22 +2243,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2266,22 +2266,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2289,22 +2289,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2312,22 +2312,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2335,22 +2335,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2358,22 +2358,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2381,22 +2381,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2404,22 +2404,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2427,22 +2427,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2450,22 +2450,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2473,22 +2473,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2496,22 +2496,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2519,22 +2519,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2542,22 +2542,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2565,22 +2565,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2588,22 +2588,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2611,22 +2611,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2634,22 +2634,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2657,22 +2657,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2680,22 +2680,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2737,22 +2737,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>217</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2766,10 +2766,10 @@
         <v>219</v>
       </c>
       <c r="D3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
         <v>220</v>
@@ -2789,10 +2789,10 @@
         <v>223</v>
       </c>
       <c r="D4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
         <v>224</v>
@@ -2812,7 +2812,7 @@
         <v>227</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -2835,10 +2835,10 @@
         <v>231</v>
       </c>
       <c r="D6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
         <v>232</v>
@@ -2858,10 +2858,10 @@
         <v>235</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
         <v>236</v>
@@ -2881,10 +2881,10 @@
         <v>239</v>
       </c>
       <c r="D8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
         <v>240</v>
@@ -2904,10 +2904,10 @@
         <v>243</v>
       </c>
       <c r="D9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>244</v>
@@ -2927,10 +2927,10 @@
         <v>247</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
         <v>248</v>
@@ -2950,10 +2950,10 @@
         <v>251</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
         <v>252</v>
@@ -2976,7 +2976,7 @@
         <v>256</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
         <v>257</v>
@@ -2996,10 +2996,10 @@
         <v>260</v>
       </c>
       <c r="D13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
         <v>261</v>
@@ -3019,10 +3019,10 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
         <v>265</v>
@@ -3042,10 +3042,10 @@
         <v>268</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
         <v>269</v>
@@ -3065,10 +3065,10 @@
         <v>272</v>
       </c>
       <c r="D16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
         <v>273</v>
@@ -3088,10 +3088,10 @@
         <v>276</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
         <v>277</v>
@@ -3145,16 +3145,16 @@
         <v>280</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
         <v>281</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3168,10 +3168,10 @@
         <v>283</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
         <v>284</v>
@@ -3191,10 +3191,10 @@
         <v>287</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
         <v>288</v>
@@ -3214,10 +3214,10 @@
         <v>291</v>
       </c>
       <c r="D5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
         <v>292</v>
@@ -3237,10 +3237,10 @@
         <v>295</v>
       </c>
       <c r="D6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
         <v>296</v>
@@ -3260,10 +3260,10 @@
         <v>299</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
         <v>300</v>
@@ -3283,10 +3283,10 @@
         <v>303</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F8" t="s">
         <v>304</v>
@@ -3306,10 +3306,10 @@
         <v>307</v>
       </c>
       <c r="D9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>308</v>
@@ -3329,7 +3329,7 @@
         <v>311</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -3352,10 +3352,10 @@
         <v>315</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>316</v>
@@ -3398,10 +3398,10 @@
         <v>324</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
         <v>325</v>
@@ -3424,7 +3424,7 @@
         <v>256</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
         <v>329</v>
@@ -3444,10 +3444,10 @@
         <v>331</v>
       </c>
       <c r="D15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
         <v>332</v>
@@ -3467,10 +3467,10 @@
         <v>335</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
         <v>336</v>
@@ -3490,10 +3490,10 @@
         <v>339</v>
       </c>
       <c r="D17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
         <v>340</v>
@@ -3513,10 +3513,10 @@
         <v>343</v>
       </c>
       <c r="D18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
         <v>344</v>
@@ -3539,7 +3539,7 @@
         <v>256</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" t="s">
         <v>348</v>
@@ -3559,10 +3559,10 @@
         <v>351</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
         <v>352</v>
@@ -3582,10 +3582,10 @@
         <v>355</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F21" t="s">
         <v>356</v>
@@ -3605,10 +3605,10 @@
         <v>359</v>
       </c>
       <c r="D22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s">
         <v>257</v>
@@ -3628,10 +3628,10 @@
         <v>362</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
         <v>363</v>
@@ -3654,7 +3654,7 @@
         <v>256</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
         <v>367</v>
@@ -3674,10 +3674,10 @@
         <v>370</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F25" t="s">
         <v>371</v>
@@ -3697,10 +3697,10 @@
         <v>374</v>
       </c>
       <c r="D26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
         <v>375</v>
@@ -3720,10 +3720,10 @@
         <v>378</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F27" t="s">
         <v>379</v>
@@ -3746,7 +3746,7 @@
         <v>256</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
         <v>383</v>
@@ -3769,7 +3769,7 @@
         <v>256</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F29" t="s">
         <v>387</v>
@@ -3789,10 +3789,10 @@
         <v>390</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
         <v>391</v>
@@ -3812,10 +3812,10 @@
         <v>394</v>
       </c>
       <c r="D31" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>395</v>
@@ -3835,10 +3835,10 @@
         <v>398</v>
       </c>
       <c r="D32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F32" t="s">
         <v>399</v>

--- a/exports/data.xlsx
+++ b/exports/data.xlsx
@@ -35,832 +35,832 @@
     <t>Обновлено</t>
   </si>
   <si>
-    <t>Текст категория • Юниоры 17-18</t>
-  </si>
-  <si>
-    <t>КРУГ 11/85</t>
-  </si>
-  <si>
-    <t>ВСЕВОЛОД БОЙЧУК</t>
+    <t>Текст категория • Мужчины</t>
+  </si>
+  <si>
+    <t>КРУГ 15/4</t>
+  </si>
+  <si>
+    <t>АНТОН СИНЦОВ</t>
+  </si>
+  <si>
+    <t>1:24:32</t>
+  </si>
+  <si>
+    <t>2026-08-08T16:36:20.904Z</t>
+  </si>
+  <si>
+    <t>Место</t>
+  </si>
+  <si>
+    <t>Участник</t>
+  </si>
+  <si>
+    <t>Номер</t>
+  </si>
+  <si>
+    <t>Возраст</t>
+  </si>
+  <si>
+    <t>Клуб</t>
+  </si>
+  <si>
+    <t>Результат</t>
+  </si>
+  <si>
+    <t>До лидера</t>
+  </si>
+  <si>
+    <t>Ильина Кристина</t>
+  </si>
+  <si>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>26 лет</t>
+  </si>
+  <si>
+    <t>Челябинская область</t>
+  </si>
+  <si>
+    <t>1:18:52</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Сайтарова Татьяна</t>
+  </si>
+  <si>
+    <t>10007</t>
+  </si>
+  <si>
+    <t>23 года</t>
+  </si>
+  <si>
+    <t>г. Москва</t>
+  </si>
+  <si>
+    <t>1:20:35</t>
+  </si>
+  <si>
+    <t>+1:43</t>
+  </si>
+  <si>
+    <t>Ушакова Александра</t>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>25 лет</t>
+  </si>
+  <si>
+    <t>Московская область</t>
+  </si>
+  <si>
+    <t>1:21:55</t>
+  </si>
+  <si>
+    <t>+3:03</t>
+  </si>
+  <si>
+    <t>Лунде Надежда</t>
+  </si>
+  <si>
+    <t>10004</t>
+  </si>
+  <si>
+    <t>г. Санкт-Петербург</t>
+  </si>
+  <si>
+    <t>1:25:14</t>
+  </si>
+  <si>
+    <t>+6:22</t>
+  </si>
+  <si>
+    <t>Тисленко Елизавета</t>
+  </si>
+  <si>
+    <t>10006</t>
+  </si>
+  <si>
+    <t>20 лет</t>
+  </si>
+  <si>
+    <t>Самарская область</t>
+  </si>
+  <si>
+    <t>1:25:43</t>
+  </si>
+  <si>
+    <t>+6:51</t>
+  </si>
+  <si>
+    <t>Миролюбова Анна</t>
+  </si>
+  <si>
+    <t>10013</t>
+  </si>
+  <si>
+    <t>Удмуртская Республика</t>
+  </si>
+  <si>
+    <t>1:26:47</t>
+  </si>
+  <si>
+    <t>+7:55</t>
+  </si>
+  <si>
+    <t>Рогозина Дарья</t>
+  </si>
+  <si>
+    <t>10017</t>
+  </si>
+  <si>
+    <t>29 лет</t>
+  </si>
+  <si>
+    <t>Чувашская Республика</t>
+  </si>
+  <si>
+    <t>1:26:56</t>
+  </si>
+  <si>
+    <t>+8:04</t>
+  </si>
+  <si>
+    <t>Калашникова Анна</t>
+  </si>
+  <si>
+    <t>10021</t>
+  </si>
+  <si>
+    <t>Республика Беларусь</t>
+  </si>
+  <si>
+    <t>1:29:26</t>
+  </si>
+  <si>
+    <t>+10:34</t>
+  </si>
+  <si>
+    <t>Тисленко Дарья</t>
+  </si>
+  <si>
+    <t>10009</t>
+  </si>
+  <si>
+    <t>1:30:17</t>
+  </si>
+  <si>
+    <t>+11:25</t>
+  </si>
+  <si>
+    <t>Карлова Алина</t>
+  </si>
+  <si>
+    <t>10002</t>
+  </si>
+  <si>
+    <t>21 год</t>
+  </si>
+  <si>
+    <t>1:32:04</t>
+  </si>
+  <si>
+    <t>+13:12</t>
+  </si>
+  <si>
+    <t>Менькова Дарья</t>
+  </si>
+  <si>
+    <t>10008</t>
+  </si>
+  <si>
+    <t>1:32:43</t>
+  </si>
+  <si>
+    <t>+13:51</t>
+  </si>
+  <si>
+    <t>Кирсанова Виктория</t>
+  </si>
+  <si>
+    <t>10014</t>
+  </si>
+  <si>
+    <t>1:11:14</t>
+  </si>
+  <si>
+    <t>-7:37</t>
+  </si>
+  <si>
+    <t>Гайбель Елизавета</t>
+  </si>
+  <si>
+    <t>10011</t>
+  </si>
+  <si>
+    <t>22 года</t>
+  </si>
+  <si>
+    <t>Свердловская область</t>
+  </si>
+  <si>
+    <t>1:13:03</t>
+  </si>
+  <si>
+    <t>-5:48</t>
+  </si>
+  <si>
+    <t>Калялина Анастасия</t>
+  </si>
+  <si>
+    <t>10010</t>
+  </si>
+  <si>
+    <t>28 лет</t>
+  </si>
+  <si>
+    <t>1:13:31</t>
+  </si>
+  <si>
+    <t>-5:20</t>
+  </si>
+  <si>
+    <t>Дудкина Карина</t>
+  </si>
+  <si>
+    <t>10018</t>
+  </si>
+  <si>
+    <t>18 лет</t>
+  </si>
+  <si>
+    <t>57:14</t>
+  </si>
+  <si>
+    <t>-21:37</t>
+  </si>
+  <si>
+    <t>Бавыкина Елизавета</t>
+  </si>
+  <si>
+    <t>10019</t>
+  </si>
+  <si>
+    <t>58:13</t>
+  </si>
+  <si>
+    <t>-20:38</t>
+  </si>
+  <si>
+    <t>Боредская Анастасия</t>
+  </si>
+  <si>
+    <t>10005</t>
+  </si>
+  <si>
+    <t>24 года</t>
+  </si>
+  <si>
+    <t>41:55</t>
+  </si>
+  <si>
+    <t>-36:56</t>
+  </si>
+  <si>
+    <t>Ахмадуллина Гузель</t>
+  </si>
+  <si>
+    <t>10020</t>
+  </si>
+  <si>
+    <t>31 год</t>
+  </si>
+  <si>
+    <t>42:03</t>
+  </si>
+  <si>
+    <t>-36:48</t>
+  </si>
+  <si>
+    <t>Гоголева Елена</t>
+  </si>
+  <si>
+    <t>10012</t>
+  </si>
+  <si>
+    <t>45 лет</t>
+  </si>
+  <si>
+    <t>44:31</t>
+  </si>
+  <si>
+    <t>-34:20</t>
+  </si>
+  <si>
+    <t>Тамонова Анна</t>
+  </si>
+  <si>
+    <t>10015</t>
+  </si>
+  <si>
+    <t>19 лет</t>
+  </si>
+  <si>
+    <t>44:45</t>
+  </si>
+  <si>
+    <t>-34:06</t>
+  </si>
+  <si>
+    <t>Кузнецова Анастасия</t>
+  </si>
+  <si>
+    <t>10016</t>
+  </si>
+  <si>
+    <t>28:16</t>
+  </si>
+  <si>
+    <t>-50:35</t>
+  </si>
+  <si>
+    <t>Синцов Антон</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>40 лет</t>
+  </si>
+  <si>
+    <t>Евграфов Евгений</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1:25:06</t>
+  </si>
+  <si>
+    <t>+0:33</t>
+  </si>
+  <si>
+    <t>Лужбин Илья</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1:25:50</t>
+  </si>
+  <si>
+    <t>+1:18</t>
+  </si>
+  <si>
+    <t>Лунде Павел</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>27 лет</t>
+  </si>
+  <si>
+    <t>1:27:07</t>
+  </si>
+  <si>
+    <t>+2:35</t>
+  </si>
+  <si>
+    <t>Шведов Ярослав</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1:27:46</t>
+  </si>
+  <si>
+    <t>+3:14</t>
+  </si>
+  <si>
+    <t>Иванов Николай</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1:28:03</t>
+  </si>
+  <si>
+    <t>+3:31</t>
+  </si>
+  <si>
+    <t>Осипов Даниил</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>1:28:22</t>
+  </si>
+  <si>
+    <t>+3:50</t>
+  </si>
+  <si>
+    <t>Балобанов Павел</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>1:29:55</t>
+  </si>
+  <si>
+    <t>+5:23</t>
+  </si>
+  <si>
+    <t>Москвин Данил</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>1:30:31</t>
+  </si>
+  <si>
+    <t>+5:59</t>
+  </si>
+  <si>
+    <t>Боредский Руслан</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1:31:13</t>
+  </si>
+  <si>
+    <t>+6:41</t>
+  </si>
+  <si>
+    <t>Филиппов Никита</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1:31:49</t>
+  </si>
+  <si>
+    <t>+7:17</t>
+  </si>
+  <si>
+    <t>Брицис Дайнис</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>1:33:12</t>
+  </si>
+  <si>
+    <t>+8:40</t>
+  </si>
+  <si>
+    <t>Селедков Иван</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>41 год</t>
+  </si>
+  <si>
+    <t>1:33:37</t>
+  </si>
+  <si>
+    <t>+9:04</t>
+  </si>
+  <si>
+    <t>Гоголев Максим</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>43 года</t>
+  </si>
+  <si>
+    <t>1:34:07</t>
+  </si>
+  <si>
+    <t>+9:35</t>
+  </si>
+  <si>
+    <t>Романов Иван</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1:35:00</t>
+  </si>
+  <si>
+    <t>+10:28</t>
+  </si>
+  <si>
+    <t>Марахтанов Глеб</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>1:07:49</t>
+  </si>
+  <si>
+    <t>-16:42</t>
+  </si>
+  <si>
+    <t>Малышко Максим</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>1:07:57</t>
+  </si>
+  <si>
+    <t>-16:34</t>
+  </si>
+  <si>
+    <t>Алексанин Данила</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>54:54</t>
+  </si>
+  <si>
+    <t>-29:37</t>
+  </si>
+  <si>
+    <t>Жидков Леон</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>55:46</t>
+  </si>
+  <si>
+    <t>-28:45</t>
+  </si>
+  <si>
+    <t>Кудрин Алексей</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>56:41</t>
+  </si>
+  <si>
+    <t>-27:50</t>
+  </si>
+  <si>
+    <t>Голубев Дмитрий</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>44:00</t>
+  </si>
+  <si>
+    <t>-40:31</t>
+  </si>
+  <si>
+    <t>Барнатович Владислав</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>30:44</t>
+  </si>
+  <si>
+    <t>-53:47</t>
+  </si>
+  <si>
+    <t>Семенова Элина</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>17 лет</t>
+  </si>
+  <si>
+    <t>1:04:47</t>
+  </si>
+  <si>
+    <t>Тимошенко Полина</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1:06:02</t>
+  </si>
+  <si>
+    <t>+1:14</t>
+  </si>
+  <si>
+    <t>Викторова Виктория</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1:07:56</t>
+  </si>
+  <si>
+    <t>+3:09</t>
+  </si>
+  <si>
+    <t>Зорина Марина</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>1:08:39</t>
+  </si>
+  <si>
+    <t>+3:52</t>
+  </si>
+  <si>
+    <t>Аветисова Ксения</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>1:09:07</t>
+  </si>
+  <si>
+    <t>+4:20</t>
+  </si>
+  <si>
+    <t>Келлер Софья</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1:09:20</t>
+  </si>
+  <si>
+    <t>+4:32</t>
+  </si>
+  <si>
+    <t>Сухорученкова Мария</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>1:10:31</t>
+  </si>
+  <si>
+    <t>+5:44</t>
+  </si>
+  <si>
+    <t>Картинина Дарья</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>1:14:49</t>
+  </si>
+  <si>
+    <t>+10:01</t>
+  </si>
+  <si>
+    <t>Парусова Елена</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>1:17:29</t>
+  </si>
+  <si>
+    <t>+12:41</t>
+  </si>
+  <si>
+    <t>Ростовщикова София</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>56:40</t>
+  </si>
+  <si>
+    <t>-8:06</t>
+  </si>
+  <si>
+    <t>Никитина Кристина</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>16 лет</t>
+  </si>
+  <si>
+    <t>1:00:16</t>
+  </si>
+  <si>
+    <t>-4:31</t>
+  </si>
+  <si>
+    <t>Чернышева Карина</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>1:01:07</t>
+  </si>
+  <si>
+    <t>-3:39</t>
+  </si>
+  <si>
+    <t>Косарева Арина</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>42:13</t>
+  </si>
+  <si>
+    <t>-22:33</t>
+  </si>
+  <si>
+    <t>Пинегина Александра</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>43:01</t>
+  </si>
+  <si>
+    <t>-21:45</t>
+  </si>
+  <si>
+    <t>Егорова Виктория</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>43:36</t>
+  </si>
+  <si>
+    <t>-21:10</t>
+  </si>
+  <si>
+    <t>Гармаш Анастасия</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>28:34</t>
+  </si>
+  <si>
+    <t>-36:13</t>
+  </si>
+  <si>
+    <t>Бойчук Всеволод</t>
+  </si>
+  <si>
+    <t>1002</t>
   </si>
   <si>
     <t>1:04:09</t>
-  </si>
-  <si>
-    <t>2026-08-08T01:08:09.743Z</t>
-  </si>
-  <si>
-    <t>Место</t>
-  </si>
-  <si>
-    <t>Участник</t>
-  </si>
-  <si>
-    <t>Номер</t>
-  </si>
-  <si>
-    <t>Возраст</t>
-  </si>
-  <si>
-    <t>Клуб</t>
-  </si>
-  <si>
-    <t>Результат</t>
-  </si>
-  <si>
-    <t>До лидера</t>
-  </si>
-  <si>
-    <t>Ильина Кристина</t>
-  </si>
-  <si>
-    <t>10003</t>
-  </si>
-  <si>
-    <t>26 лет</t>
-  </si>
-  <si>
-    <t>Челябинская область</t>
-  </si>
-  <si>
-    <t>1:18:52</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Сайтарова Татьяна</t>
-  </si>
-  <si>
-    <t>10007</t>
-  </si>
-  <si>
-    <t>23 года</t>
-  </si>
-  <si>
-    <t>г. Москва</t>
-  </si>
-  <si>
-    <t>1:20:35</t>
-  </si>
-  <si>
-    <t>+1:43</t>
-  </si>
-  <si>
-    <t>Ушакова Александра</t>
-  </si>
-  <si>
-    <t>10001</t>
-  </si>
-  <si>
-    <t>25 лет</t>
-  </si>
-  <si>
-    <t>Московская область</t>
-  </si>
-  <si>
-    <t>1:21:55</t>
-  </si>
-  <si>
-    <t>+3:03</t>
-  </si>
-  <si>
-    <t>Лунде Надежда</t>
-  </si>
-  <si>
-    <t>10004</t>
-  </si>
-  <si>
-    <t>г. Санкт-Петербург</t>
-  </si>
-  <si>
-    <t>1:25:14</t>
-  </si>
-  <si>
-    <t>+6:22</t>
-  </si>
-  <si>
-    <t>Тисленко Елизавета</t>
-  </si>
-  <si>
-    <t>10006</t>
-  </si>
-  <si>
-    <t>20 лет</t>
-  </si>
-  <si>
-    <t>Самарская область</t>
-  </si>
-  <si>
-    <t>1:25:43</t>
-  </si>
-  <si>
-    <t>+6:51</t>
-  </si>
-  <si>
-    <t>Миролюбова Анна</t>
-  </si>
-  <si>
-    <t>10013</t>
-  </si>
-  <si>
-    <t>Удмуртская Республика</t>
-  </si>
-  <si>
-    <t>1:26:47</t>
-  </si>
-  <si>
-    <t>+7:55</t>
-  </si>
-  <si>
-    <t>Рогозина Дарья</t>
-  </si>
-  <si>
-    <t>10017</t>
-  </si>
-  <si>
-    <t>29 лет</t>
-  </si>
-  <si>
-    <t>Чувашская Республика</t>
-  </si>
-  <si>
-    <t>1:26:56</t>
-  </si>
-  <si>
-    <t>+8:04</t>
-  </si>
-  <si>
-    <t>Калашникова Анна</t>
-  </si>
-  <si>
-    <t>10021</t>
-  </si>
-  <si>
-    <t>Республика Беларусь</t>
-  </si>
-  <si>
-    <t>1:29:26</t>
-  </si>
-  <si>
-    <t>+10:34</t>
-  </si>
-  <si>
-    <t>Тисленко Дарья</t>
-  </si>
-  <si>
-    <t>10009</t>
-  </si>
-  <si>
-    <t>1:30:17</t>
-  </si>
-  <si>
-    <t>+11:25</t>
-  </si>
-  <si>
-    <t>Карлова Алина</t>
-  </si>
-  <si>
-    <t>10002</t>
-  </si>
-  <si>
-    <t>21 год</t>
-  </si>
-  <si>
-    <t>1:32:04</t>
-  </si>
-  <si>
-    <t>+13:12</t>
-  </si>
-  <si>
-    <t>Менькова Дарья</t>
-  </si>
-  <si>
-    <t>10008</t>
-  </si>
-  <si>
-    <t>1:32:43</t>
-  </si>
-  <si>
-    <t>+13:51</t>
-  </si>
-  <si>
-    <t>Кирсанова Виктория</t>
-  </si>
-  <si>
-    <t>10014</t>
-  </si>
-  <si>
-    <t>1:11:14</t>
-  </si>
-  <si>
-    <t>-7:37</t>
-  </si>
-  <si>
-    <t>Гайбель Елизавета</t>
-  </si>
-  <si>
-    <t>10011</t>
-  </si>
-  <si>
-    <t>22 года</t>
-  </si>
-  <si>
-    <t>Свердловская область</t>
-  </si>
-  <si>
-    <t>1:13:03</t>
-  </si>
-  <si>
-    <t>-5:48</t>
-  </si>
-  <si>
-    <t>Калялина Анастасия</t>
-  </si>
-  <si>
-    <t>10010</t>
-  </si>
-  <si>
-    <t>28 лет</t>
-  </si>
-  <si>
-    <t>1:13:31</t>
-  </si>
-  <si>
-    <t>-5:20</t>
-  </si>
-  <si>
-    <t>Дудкина Карина</t>
-  </si>
-  <si>
-    <t>10018</t>
-  </si>
-  <si>
-    <t>18 лет</t>
-  </si>
-  <si>
-    <t>57:14</t>
-  </si>
-  <si>
-    <t>-21:37</t>
-  </si>
-  <si>
-    <t>Бавыкина Елизавета</t>
-  </si>
-  <si>
-    <t>10019</t>
-  </si>
-  <si>
-    <t>58:13</t>
-  </si>
-  <si>
-    <t>-20:38</t>
-  </si>
-  <si>
-    <t>Боредская Анастасия</t>
-  </si>
-  <si>
-    <t>10005</t>
-  </si>
-  <si>
-    <t>24 года</t>
-  </si>
-  <si>
-    <t>41:55</t>
-  </si>
-  <si>
-    <t>-36:56</t>
-  </si>
-  <si>
-    <t>Ахмадуллина Гузель</t>
-  </si>
-  <si>
-    <t>10020</t>
-  </si>
-  <si>
-    <t>31 год</t>
-  </si>
-  <si>
-    <t>42:03</t>
-  </si>
-  <si>
-    <t>-36:48</t>
-  </si>
-  <si>
-    <t>Гоголева Елена</t>
-  </si>
-  <si>
-    <t>10012</t>
-  </si>
-  <si>
-    <t>45 лет</t>
-  </si>
-  <si>
-    <t>44:31</t>
-  </si>
-  <si>
-    <t>-34:20</t>
-  </si>
-  <si>
-    <t>Тамонова Анна</t>
-  </si>
-  <si>
-    <t>10015</t>
-  </si>
-  <si>
-    <t>19 лет</t>
-  </si>
-  <si>
-    <t>44:45</t>
-  </si>
-  <si>
-    <t>-34:06</t>
-  </si>
-  <si>
-    <t>Кузнецова Анастасия</t>
-  </si>
-  <si>
-    <t>10016</t>
-  </si>
-  <si>
-    <t>28:16</t>
-  </si>
-  <si>
-    <t>-50:35</t>
-  </si>
-  <si>
-    <t>Синцов Антон</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>40 лет</t>
-  </si>
-  <si>
-    <t>1:24:32</t>
-  </si>
-  <si>
-    <t>Евграфов Евгений</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>1:25:06</t>
-  </si>
-  <si>
-    <t>+0:33</t>
-  </si>
-  <si>
-    <t>Лужбин Илья</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1:25:50</t>
-  </si>
-  <si>
-    <t>+1:18</t>
-  </si>
-  <si>
-    <t>Лунде Павел</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>27 лет</t>
-  </si>
-  <si>
-    <t>1:27:07</t>
-  </si>
-  <si>
-    <t>+2:35</t>
-  </si>
-  <si>
-    <t>Шведов Ярослав</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>1:27:46</t>
-  </si>
-  <si>
-    <t>+3:14</t>
-  </si>
-  <si>
-    <t>Иванов Николай</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1:28:03</t>
-  </si>
-  <si>
-    <t>+3:31</t>
-  </si>
-  <si>
-    <t>Осипов Даниил</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1:28:22</t>
-  </si>
-  <si>
-    <t>+3:50</t>
-  </si>
-  <si>
-    <t>Балобанов Павел</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>1:29:55</t>
-  </si>
-  <si>
-    <t>+5:23</t>
-  </si>
-  <si>
-    <t>Москвин Данил</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>1:30:31</t>
-  </si>
-  <si>
-    <t>+5:59</t>
-  </si>
-  <si>
-    <t>Боредский Руслан</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>1:31:13</t>
-  </si>
-  <si>
-    <t>+6:41</t>
-  </si>
-  <si>
-    <t>Филиппов Никита</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1:31:49</t>
-  </si>
-  <si>
-    <t>+7:17</t>
-  </si>
-  <si>
-    <t>Брицис Дайнис</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>1:33:12</t>
-  </si>
-  <si>
-    <t>+8:40</t>
-  </si>
-  <si>
-    <t>Селедков Иван</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>41 год</t>
-  </si>
-  <si>
-    <t>1:33:37</t>
-  </si>
-  <si>
-    <t>+9:04</t>
-  </si>
-  <si>
-    <t>Гоголев Максим</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>43 года</t>
-  </si>
-  <si>
-    <t>1:34:07</t>
-  </si>
-  <si>
-    <t>+9:35</t>
-  </si>
-  <si>
-    <t>Романов Иван</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1:35:00</t>
-  </si>
-  <si>
-    <t>+10:28</t>
-  </si>
-  <si>
-    <t>Марахтанов Глеб</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>1:07:49</t>
-  </si>
-  <si>
-    <t>-16:42</t>
-  </si>
-  <si>
-    <t>Малышко Максим</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>1:07:57</t>
-  </si>
-  <si>
-    <t>-16:34</t>
-  </si>
-  <si>
-    <t>Алексанин Данила</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>54:54</t>
-  </si>
-  <si>
-    <t>-29:37</t>
-  </si>
-  <si>
-    <t>Жидков Леон</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>55:46</t>
-  </si>
-  <si>
-    <t>-28:45</t>
-  </si>
-  <si>
-    <t>Кудрин Алексей</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>56:41</t>
-  </si>
-  <si>
-    <t>-27:50</t>
-  </si>
-  <si>
-    <t>Голубев Дмитрий</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>44:00</t>
-  </si>
-  <si>
-    <t>-40:31</t>
-  </si>
-  <si>
-    <t>Барнатович Владислав</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>30:44</t>
-  </si>
-  <si>
-    <t>-53:47</t>
-  </si>
-  <si>
-    <t>Семенова Элина</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>17 лет</t>
-  </si>
-  <si>
-    <t>1:04:47</t>
-  </si>
-  <si>
-    <t>Тимошенко Полина</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1:06:02</t>
-  </si>
-  <si>
-    <t>+1:14</t>
-  </si>
-  <si>
-    <t>Викторова Виктория</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1:07:56</t>
-  </si>
-  <si>
-    <t>+3:09</t>
-  </si>
-  <si>
-    <t>Зорина Марина</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>1:08:39</t>
-  </si>
-  <si>
-    <t>+3:52</t>
-  </si>
-  <si>
-    <t>Аветисова Ксения</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>1:09:07</t>
-  </si>
-  <si>
-    <t>+4:20</t>
-  </si>
-  <si>
-    <t>Келлер Софья</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1:09:20</t>
-  </si>
-  <si>
-    <t>+4:32</t>
-  </si>
-  <si>
-    <t>Сухорученкова Мария</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>1:10:31</t>
-  </si>
-  <si>
-    <t>+5:44</t>
-  </si>
-  <si>
-    <t>Картинина Дарья</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>1:14:49</t>
-  </si>
-  <si>
-    <t>+10:01</t>
-  </si>
-  <si>
-    <t>Парусова Елена</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>1:17:29</t>
-  </si>
-  <si>
-    <t>+12:41</t>
-  </si>
-  <si>
-    <t>Ростовщикова София</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>56:40</t>
-  </si>
-  <si>
-    <t>-8:06</t>
-  </si>
-  <si>
-    <t>Никитина Кристина</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>16 лет</t>
-  </si>
-  <si>
-    <t>1:00:16</t>
-  </si>
-  <si>
-    <t>-4:31</t>
-  </si>
-  <si>
-    <t>Чернышева Карина</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>1:01:07</t>
-  </si>
-  <si>
-    <t>-3:39</t>
-  </si>
-  <si>
-    <t>Косарева Арина</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>42:13</t>
-  </si>
-  <si>
-    <t>-22:33</t>
-  </si>
-  <si>
-    <t>Пинегина Александра</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>43:01</t>
-  </si>
-  <si>
-    <t>-21:45</t>
-  </si>
-  <si>
-    <t>Егорова Виктория</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>43:36</t>
-  </si>
-  <si>
-    <t>-21:10</t>
-  </si>
-  <si>
-    <t>Гармаш Анастасия</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>28:34</t>
-  </si>
-  <si>
-    <t>-36:13</t>
-  </si>
-  <si>
-    <t>Бойчук Всеволод</t>
-  </si>
-  <si>
-    <t>1002</t>
   </si>
   <si>
     <t>Гвоздарев Вадим</t>
@@ -1632,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>1002</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -2209,7 +2209,7 @@
         <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
@@ -2220,10 +2220,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
         <v>128</v>
-      </c>
-      <c r="C3" t="s">
-        <v>129</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
@@ -2232,10 +2232,10 @@
         <v>55</v>
       </c>
       <c r="F3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" t="s">
         <v>130</v>
-      </c>
-      <c r="G3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2243,10 +2243,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" t="s">
         <v>132</v>
-      </c>
-      <c r="C4" t="s">
-        <v>133</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -2255,10 +2255,10 @@
         <v>49</v>
       </c>
       <c r="F4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" t="s">
         <v>134</v>
-      </c>
-      <c r="G4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2266,22 +2266,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" t="s">
         <v>136</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>137</v>
-      </c>
-      <c r="D5" t="s">
-        <v>138</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
       </c>
       <c r="F5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G5" t="s">
         <v>139</v>
-      </c>
-      <c r="G5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2289,10 +2289,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" t="s">
         <v>141</v>
-      </c>
-      <c r="C6" t="s">
-        <v>142</v>
       </c>
       <c r="D6" t="s">
         <v>69</v>
@@ -2301,10 +2301,10 @@
         <v>33</v>
       </c>
       <c r="F6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" t="s">
         <v>143</v>
-      </c>
-      <c r="G6" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2312,10 +2312,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" t="s">
         <v>145</v>
-      </c>
-      <c r="C7" t="s">
-        <v>146</v>
       </c>
       <c r="D7" t="s">
         <v>102</v>
@@ -2324,10 +2324,10 @@
         <v>38</v>
       </c>
       <c r="F7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G7" t="s">
         <v>147</v>
-      </c>
-      <c r="G7" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2335,10 +2335,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" t="s">
         <v>149</v>
-      </c>
-      <c r="C8" t="s">
-        <v>150</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
@@ -2347,10 +2347,10 @@
         <v>33</v>
       </c>
       <c r="F8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" t="s">
         <v>151</v>
-      </c>
-      <c r="G8" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2358,10 +2358,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" t="s">
         <v>153</v>
-      </c>
-      <c r="C9" t="s">
-        <v>154</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -2370,10 +2370,10 @@
         <v>49</v>
       </c>
       <c r="F9" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9" t="s">
         <v>155</v>
-      </c>
-      <c r="G9" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2381,10 +2381,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" t="s">
         <v>157</v>
-      </c>
-      <c r="C10" t="s">
-        <v>158</v>
       </c>
       <c r="D10" t="s">
         <v>88</v>
@@ -2393,10 +2393,10 @@
         <v>49</v>
       </c>
       <c r="F10" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" t="s">
         <v>159</v>
-      </c>
-      <c r="G10" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2404,10 +2404,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" t="s">
         <v>161</v>
-      </c>
-      <c r="C11" t="s">
-        <v>162</v>
       </c>
       <c r="D11" t="s">
         <v>107</v>
@@ -2416,10 +2416,10 @@
         <v>38</v>
       </c>
       <c r="F11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G11" t="s">
         <v>163</v>
-      </c>
-      <c r="G11" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2427,10 +2427,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" t="s">
         <v>165</v>
-      </c>
-      <c r="C12" t="s">
-        <v>166</v>
       </c>
       <c r="D12" t="s">
         <v>82</v>
@@ -2439,10 +2439,10 @@
         <v>83</v>
       </c>
       <c r="F12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G12" t="s">
         <v>167</v>
-      </c>
-      <c r="G12" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2450,10 +2450,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" t="s">
         <v>169</v>
-      </c>
-      <c r="C13" t="s">
-        <v>170</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
@@ -2462,10 +2462,10 @@
         <v>60</v>
       </c>
       <c r="F13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G13" t="s">
         <v>171</v>
-      </c>
-      <c r="G13" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2473,22 +2473,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" t="s">
         <v>173</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>174</v>
-      </c>
-      <c r="D14" t="s">
-        <v>175</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
       </c>
       <c r="F14" t="s">
+        <v>175</v>
+      </c>
+      <c r="G14" t="s">
         <v>176</v>
-      </c>
-      <c r="G14" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2496,22 +2496,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" t="s">
         <v>178</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>179</v>
-      </c>
-      <c r="D15" t="s">
-        <v>180</v>
       </c>
       <c r="E15" t="s">
         <v>44</v>
       </c>
       <c r="F15" t="s">
+        <v>180</v>
+      </c>
+      <c r="G15" t="s">
         <v>181</v>
-      </c>
-      <c r="G15" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2519,10 +2519,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" t="s">
         <v>183</v>
-      </c>
-      <c r="C16" t="s">
-        <v>184</v>
       </c>
       <c r="D16" t="s">
         <v>82</v>
@@ -2531,10 +2531,10 @@
         <v>21</v>
       </c>
       <c r="F16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G16" t="s">
         <v>185</v>
-      </c>
-      <c r="G16" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2542,10 +2542,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C17" t="s">
         <v>187</v>
-      </c>
-      <c r="C17" t="s">
-        <v>188</v>
       </c>
       <c r="D17" t="s">
         <v>117</v>
@@ -2554,10 +2554,10 @@
         <v>38</v>
       </c>
       <c r="F17" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" t="s">
         <v>189</v>
-      </c>
-      <c r="G17" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2565,10 +2565,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" t="s">
         <v>191</v>
-      </c>
-      <c r="C18" t="s">
-        <v>192</v>
       </c>
       <c r="D18" t="s">
         <v>43</v>
@@ -2577,10 +2577,10 @@
         <v>60</v>
       </c>
       <c r="F18" t="s">
+        <v>192</v>
+      </c>
+      <c r="G18" t="s">
         <v>193</v>
-      </c>
-      <c r="G18" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2588,10 +2588,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" t="s">
         <v>195</v>
-      </c>
-      <c r="C19" t="s">
-        <v>196</v>
       </c>
       <c r="D19" t="s">
         <v>43</v>
@@ -2600,10 +2600,10 @@
         <v>38</v>
       </c>
       <c r="F19" t="s">
+        <v>196</v>
+      </c>
+      <c r="G19" t="s">
         <v>197</v>
-      </c>
-      <c r="G19" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2611,10 +2611,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C20" t="s">
         <v>199</v>
-      </c>
-      <c r="C20" t="s">
-        <v>200</v>
       </c>
       <c r="D20" t="s">
         <v>69</v>
@@ -2623,10 +2623,10 @@
         <v>38</v>
       </c>
       <c r="F20" t="s">
+        <v>200</v>
+      </c>
+      <c r="G20" t="s">
         <v>201</v>
-      </c>
-      <c r="G20" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2634,10 +2634,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>202</v>
+      </c>
+      <c r="C21" t="s">
         <v>203</v>
-      </c>
-      <c r="C21" t="s">
-        <v>204</v>
       </c>
       <c r="D21" t="s">
         <v>88</v>
@@ -2646,10 +2646,10 @@
         <v>44</v>
       </c>
       <c r="F21" t="s">
+        <v>204</v>
+      </c>
+      <c r="G21" t="s">
         <v>205</v>
-      </c>
-      <c r="G21" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2657,10 +2657,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>206</v>
+      </c>
+      <c r="C22" t="s">
         <v>207</v>
-      </c>
-      <c r="C22" t="s">
-        <v>208</v>
       </c>
       <c r="D22" t="s">
         <v>117</v>
@@ -2669,10 +2669,10 @@
         <v>33</v>
       </c>
       <c r="F22" t="s">
+        <v>208</v>
+      </c>
+      <c r="G22" t="s">
         <v>209</v>
-      </c>
-      <c r="G22" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2680,10 +2680,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" t="s">
         <v>211</v>
-      </c>
-      <c r="C23" t="s">
-        <v>212</v>
       </c>
       <c r="D23" t="s">
         <v>82</v>
@@ -2692,10 +2692,10 @@
         <v>60</v>
       </c>
       <c r="F23" t="s">
+        <v>212</v>
+      </c>
+      <c r="G23" t="s">
         <v>213</v>
-      </c>
-      <c r="G23" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2737,19 +2737,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" t="s">
         <v>215</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>216</v>
-      </c>
-      <c r="D2" t="s">
-        <v>217</v>
       </c>
       <c r="E2" t="s">
         <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
@@ -2760,22 +2760,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" t="s">
         <v>219</v>
       </c>
-      <c r="C3" t="s">
-        <v>220</v>
-      </c>
       <c r="D3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E3" t="s">
         <v>27</v>
       </c>
       <c r="F3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G3" t="s">
         <v>221</v>
-      </c>
-      <c r="G3" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2783,22 +2783,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" t="s">
         <v>223</v>
       </c>
-      <c r="C4" t="s">
-        <v>224</v>
-      </c>
       <c r="D4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E4" t="s">
         <v>38</v>
       </c>
       <c r="F4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G4" t="s">
         <v>225</v>
-      </c>
-      <c r="G4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2806,10 +2806,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" t="s">
         <v>227</v>
-      </c>
-      <c r="C5" t="s">
-        <v>228</v>
       </c>
       <c r="D5" t="s">
         <v>93</v>
@@ -2818,10 +2818,10 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
+        <v>228</v>
+      </c>
+      <c r="G5" t="s">
         <v>229</v>
-      </c>
-      <c r="G5" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2829,22 +2829,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
         <v>231</v>
       </c>
-      <c r="C6" t="s">
-        <v>232</v>
-      </c>
       <c r="D6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
       </c>
       <c r="F6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" t="s">
         <v>233</v>
-      </c>
-      <c r="G6" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2852,10 +2852,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" t="s">
         <v>235</v>
-      </c>
-      <c r="C7" t="s">
-        <v>236</v>
       </c>
       <c r="D7" t="s">
         <v>93</v>
@@ -2864,10 +2864,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
+        <v>236</v>
+      </c>
+      <c r="G7" t="s">
         <v>237</v>
-      </c>
-      <c r="G7" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2875,22 +2875,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" t="s">
         <v>239</v>
       </c>
-      <c r="C8" t="s">
-        <v>240</v>
-      </c>
       <c r="D8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
       </c>
       <c r="F8" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" t="s">
         <v>241</v>
-      </c>
-      <c r="G8" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2898,22 +2898,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" t="s">
         <v>243</v>
       </c>
-      <c r="C9" t="s">
-        <v>244</v>
-      </c>
       <c r="D9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
       </c>
       <c r="F9" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" t="s">
         <v>245</v>
-      </c>
-      <c r="G9" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2921,10 +2921,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" t="s">
         <v>247</v>
-      </c>
-      <c r="C10" t="s">
-        <v>248</v>
       </c>
       <c r="D10" t="s">
         <v>93</v>
@@ -2933,10 +2933,10 @@
         <v>55</v>
       </c>
       <c r="F10" t="s">
+        <v>248</v>
+      </c>
+      <c r="G10" t="s">
         <v>249</v>
-      </c>
-      <c r="G10" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2944,10 +2944,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C11" t="s">
         <v>251</v>
-      </c>
-      <c r="C11" t="s">
-        <v>252</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
@@ -2956,10 +2956,10 @@
         <v>55</v>
       </c>
       <c r="F11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G11" t="s">
         <v>253</v>
-      </c>
-      <c r="G11" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2967,22 +2967,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" t="s">
         <v>255</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>256</v>
-      </c>
-      <c r="D12" t="s">
-        <v>257</v>
       </c>
       <c r="E12" t="s">
         <v>55</v>
       </c>
       <c r="F12" t="s">
+        <v>257</v>
+      </c>
+      <c r="G12" t="s">
         <v>258</v>
-      </c>
-      <c r="G12" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2990,22 +2990,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>259</v>
+      </c>
+      <c r="C13" t="s">
         <v>260</v>
       </c>
-      <c r="C13" t="s">
-        <v>261</v>
-      </c>
       <c r="D13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E13" t="s">
         <v>49</v>
       </c>
       <c r="F13" t="s">
+        <v>261</v>
+      </c>
+      <c r="G13" t="s">
         <v>262</v>
-      </c>
-      <c r="G13" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3013,22 +3013,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14" t="s">
         <v>264</v>
       </c>
-      <c r="C14" t="s">
-        <v>265</v>
-      </c>
       <c r="D14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E14" t="s">
         <v>38</v>
       </c>
       <c r="F14" t="s">
+        <v>265</v>
+      </c>
+      <c r="G14" t="s">
         <v>266</v>
-      </c>
-      <c r="G14" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3036,10 +3036,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C15" t="s">
         <v>268</v>
-      </c>
-      <c r="C15" t="s">
-        <v>269</v>
       </c>
       <c r="D15" t="s">
         <v>93</v>
@@ -3048,10 +3048,10 @@
         <v>55</v>
       </c>
       <c r="F15" t="s">
+        <v>269</v>
+      </c>
+      <c r="G15" t="s">
         <v>270</v>
-      </c>
-      <c r="G15" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3059,22 +3059,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" t="s">
         <v>272</v>
       </c>
-      <c r="C16" t="s">
-        <v>273</v>
-      </c>
       <c r="D16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E16" t="s">
         <v>83</v>
       </c>
       <c r="F16" t="s">
+        <v>273</v>
+      </c>
+      <c r="G16" t="s">
         <v>274</v>
-      </c>
-      <c r="G16" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3082,10 +3082,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17" t="s">
         <v>276</v>
-      </c>
-      <c r="C17" t="s">
-        <v>277</v>
       </c>
       <c r="D17" t="s">
         <v>93</v>
@@ -3094,10 +3094,10 @@
         <v>38</v>
       </c>
       <c r="F17" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" t="s">
         <v>278</v>
-      </c>
-      <c r="G17" t="s">
-        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -3139,10 +3139,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" t="s">
         <v>280</v>
-      </c>
-      <c r="C2" t="s">
-        <v>281</v>
       </c>
       <c r="D2" t="s">
         <v>93</v>
@@ -3151,7 +3151,7 @@
         <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>281</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
@@ -3214,7 +3214,7 @@
         <v>291</v>
       </c>
       <c r="D5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -3237,7 +3237,7 @@
         <v>295</v>
       </c>
       <c r="D6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
@@ -3306,7 +3306,7 @@
         <v>307</v>
       </c>
       <c r="D9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
@@ -3375,7 +3375,7 @@
         <v>319</v>
       </c>
       <c r="D12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E12" t="s">
         <v>320</v>
@@ -3421,7 +3421,7 @@
         <v>328</v>
       </c>
       <c r="D14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E14" t="s">
         <v>55</v>
@@ -3444,7 +3444,7 @@
         <v>331</v>
       </c>
       <c r="D15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E15" t="s">
         <v>38</v>
@@ -3490,7 +3490,7 @@
         <v>339</v>
       </c>
       <c r="D17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E17" t="s">
         <v>60</v>
@@ -3513,7 +3513,7 @@
         <v>343</v>
       </c>
       <c r="D18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -3536,7 +3536,7 @@
         <v>347</v>
       </c>
       <c r="D19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E19" t="s">
         <v>83</v>
@@ -3605,13 +3605,13 @@
         <v>359</v>
       </c>
       <c r="D22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E22" t="s">
         <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G22" t="s">
         <v>360</v>
@@ -3651,7 +3651,7 @@
         <v>366</v>
       </c>
       <c r="D24" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E24" t="s">
         <v>38</v>
@@ -3697,7 +3697,7 @@
         <v>374</v>
       </c>
       <c r="D26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E26" t="s">
         <v>38</v>
@@ -3743,7 +3743,7 @@
         <v>382</v>
       </c>
       <c r="D28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E28" t="s">
         <v>55</v>
@@ -3766,7 +3766,7 @@
         <v>386</v>
       </c>
       <c r="D29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E29" t="s">
         <v>83</v>
@@ -3812,7 +3812,7 @@
         <v>394</v>
       </c>
       <c r="D31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E31" t="s">
         <v>33</v>
@@ -3835,7 +3835,7 @@
         <v>398</v>
       </c>
       <c r="D32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E32" t="s">
         <v>83</v>

--- a/exports/data.xlsx
+++ b/exports/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="142">
   <si>
     <t>Категория</t>
   </si>
@@ -35,19 +35,13 @@
     <t>Обновлено</t>
   </si>
   <si>
-    <t>Кубок России • Мужчины</t>
-  </si>
-  <si>
-    <t>КРУГ 1/3</t>
-  </si>
-  <si>
-    <t>ТЕСТ ЛИДЕР</t>
+    <t>Кубок России • Женщины</t>
+  </si>
+  <si>
+    <t>КРУГ 0/6</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2026-08-08T21:49:56.913Z</t>
   </si>
   <si>
     <t>Место</t>
@@ -861,13 +855,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -883,439 +877,439 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
         <v>50</v>
       </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s">
-        <v>52</v>
-      </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
         <v>55</v>
       </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
         <v>58</v>
       </c>
-      <c r="C15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1331,784 +1325,784 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
-      </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="s">
         <v>72</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>73</v>
       </c>
-      <c r="D3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" t="s">
-        <v>75</v>
-      </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
         <v>80</v>
       </c>
-      <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
         <v>83</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>84</v>
       </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>86</v>
-      </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" t="s">
         <v>101</v>
       </c>
-      <c r="C15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" t="s">
         <v>106</v>
       </c>
-      <c r="C17" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
-      </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" t="s">
         <v>123</v>
       </c>
-      <c r="C25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" t="s">
-        <v>125</v>
-      </c>
       <c r="E25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2124,439 +2118,439 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
         <v>50</v>
       </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s">
-        <v>52</v>
-      </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
         <v>55</v>
       </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
         <v>58</v>
       </c>
-      <c r="C15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2572,439 +2566,439 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
         <v>50</v>
       </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s">
-        <v>52</v>
-      </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
         <v>55</v>
       </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
         <v>58</v>
       </c>
-      <c r="C15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
